--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="430" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ED4EAA6-3D99-469C-BAF7-574C0B89A8E4}"/>
+  <xr:revisionPtr revIDLastSave="445" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A5304A2-057F-4C45-92EB-29727FD3CADA}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="118">
   <si>
     <t>Date</t>
   </si>
@@ -337,12 +350,6 @@
     <t>Delayed - 14-09-26</t>
   </si>
   <si>
-    <t>Delayed -01.09.26/10.09.26</t>
-  </si>
-  <si>
-    <t>Delayed - 30.08.26/15.09.26</t>
-  </si>
-  <si>
     <t>Delayed - 15.09.26</t>
   </si>
   <si>
@@ -367,13 +374,19 @@
     <t>Delayed - 30.08.26/10.09.26/20.09.26</t>
   </si>
   <si>
-    <t>Delayed - 28.08.26/04.09.26/15.09.26</t>
-  </si>
-  <si>
     <t>Delayed - 10.09.26/20.09.26</t>
   </si>
   <si>
     <t>Delayed - 16.09.26</t>
+  </si>
+  <si>
+    <t>Delayed -01.09.26/10.09.26/25.09.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eco Hopper erection </t>
+  </si>
+  <si>
+    <t>Delayed - 30.08.26/15.09.26/25.09.26</t>
   </si>
 </sst>
 </file>
@@ -452,6 +465,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -739,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -946,7 +963,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
@@ -1205,7 +1222,7 @@
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D35" t="s">
         <v>19</v>
@@ -1275,7 +1292,7 @@
         <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D40" t="s">
         <v>16</v>
@@ -1413,7 +1430,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="B52" t="s">
         <v>69</v>
@@ -1427,13 +1444,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B53" t="s">
         <v>70</v>
       </c>
       <c r="C53" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D53" t="s">
         <v>16</v>
@@ -1441,7 +1458,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
-        <v>46305</v>
+        <v>46326</v>
       </c>
       <c r="B54" t="s">
         <v>71</v>
@@ -1452,7 +1469,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
-        <v>46320</v>
+        <v>46326</v>
       </c>
       <c r="B55" t="s">
         <v>72</v>
@@ -1502,7 +1519,7 @@
         <v>76</v>
       </c>
       <c r="C59" t="s">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="D59" t="s">
         <v>16</v>
@@ -1524,7 +1541,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
-        <v>46291</v>
+        <v>46305</v>
       </c>
       <c r="B61" t="s">
         <v>78</v>
@@ -1571,13 +1588,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
-        <v>46285</v>
+        <v>46290</v>
       </c>
       <c r="B65" t="s">
         <v>83</v>
       </c>
       <c r="C65" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -1585,7 +1602,7 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A66" s="2">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>84</v>
@@ -1644,7 +1661,7 @@
         <v>88</v>
       </c>
       <c r="C70" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D70" t="s">
         <v>17</v>
@@ -1658,7 +1675,7 @@
         <v>89</v>
       </c>
       <c r="C71" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D71" t="s">
         <v>17</v>
@@ -1672,7 +1689,7 @@
         <v>90</v>
       </c>
       <c r="C72" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D72" t="s">
         <v>17</v>
@@ -1680,13 +1697,13 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B73" t="s">
         <v>91</v>
       </c>
       <c r="C73" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D73" t="s">
         <v>17</v>
@@ -1700,7 +1717,7 @@
         <v>92</v>
       </c>
       <c r="C74" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D74" t="s">
         <v>17</v>
@@ -1722,7 +1739,7 @@
         <v>46341</v>
       </c>
       <c r="B76" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D76" t="s">
         <v>16</v>
@@ -1733,7 +1750,7 @@
         <v>46356</v>
       </c>
       <c r="B77" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D77" t="s">
         <v>16</v>
@@ -1744,7 +1761,7 @@
         <v>46351</v>
       </c>
       <c r="B78" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D78" t="s">
         <v>16</v>
@@ -1755,9 +1772,20 @@
         <v>46326</v>
       </c>
       <c r="B79" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A80" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B80" t="s">
+        <v>116</v>
+      </c>
+      <c r="D80" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="445" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A5304A2-057F-4C45-92EB-29727FD3CADA}"/>
+  <xr:revisionPtr revIDLastSave="446" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EC73659-2317-417D-AFEC-378FF0008CBD}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -44,9 +44,6 @@
     <t>TG Box up - Target completion</t>
   </si>
   <si>
-    <t>Meeting with BHEL Dir Power</t>
-  </si>
-  <si>
     <t>UNIT#3 hot box Side plate erection by 03.08.26</t>
   </si>
   <si>
@@ -87,9 +84,6 @@
   </si>
   <si>
     <t>EED</t>
-  </si>
-  <si>
-    <t>P&amp;S</t>
   </si>
   <si>
     <t>CCD</t>
@@ -465,10 +459,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -756,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -773,10 +763,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
@@ -784,66 +774,66 @@
         <v>46259</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
-        <v>46251</v>
+        <v>46280</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
@@ -851,13 +841,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
-        <v>46280</v>
+        <v>46269</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -865,260 +855,260 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
-        <v>46269</v>
+        <v>46251</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
-        <v>46251</v>
+        <v>46310</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
-        <v>46310</v>
+        <v>46295</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
-        <v>46295</v>
+        <v>46356</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
-        <v>46356</v>
+        <v>46295</v>
       </c>
       <c r="B14" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
-        <v>46295</v>
+        <v>46280</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
-        <v>46280</v>
+        <v>46344</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
-        <v>46344</v>
+        <v>46341</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
-      <c r="C17" t="s">
-        <v>65</v>
-      </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
-        <v>46341</v>
+        <v>46381</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
-        <v>46381</v>
+        <v>46425</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
-        <v>46425</v>
+        <v>46443</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
-        <v>46443</v>
+        <v>46461</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
-        <v>46461</v>
+        <v>46254</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
-        <v>46254</v>
+        <v>45991</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
-        <v>45991</v>
+        <v>46321</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
-        <v>46321</v>
+        <v>46290</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
-        <v>46290</v>
+        <v>46402</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
-        <v>46402</v>
+        <v>46265</v>
       </c>
       <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
         <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
-        <v>46265</v>
+        <v>46270</v>
       </c>
       <c r="B28" t="s">
         <v>36</v>
@@ -1127,7 +1117,7 @@
         <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
@@ -1141,263 +1131,260 @@
         <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="B30" t="s">
         <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A31" s="2">
         <v>46275</v>
       </c>
-      <c r="B31" t="s">
-        <v>42</v>
+      <c r="B31" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B32" s="3" t="s">
+        <v>46310</v>
+      </c>
+      <c r="B32" t="s">
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
-        <v>46310</v>
+        <v>46285</v>
       </c>
       <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A34" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C33" t="s">
-        <v>96</v>
-      </c>
-      <c r="D33" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A34" s="2">
-        <v>46285</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B35" t="s">
         <v>46</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>97</v>
       </c>
-      <c r="D34" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A35" s="2">
-        <v>46295</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C35" t="s">
-        <v>112</v>
-      </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
-        <v>46290</v>
+        <v>46254</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
-        <v>46254</v>
+        <v>46272</v>
       </c>
       <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A38" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A38" s="2">
-        <v>46272</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B39" t="s">
         <v>50</v>
       </c>
-      <c r="C38" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A39" s="2">
-        <v>46285</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
-        <v>46305</v>
+        <v>46320</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
-        <v>46320</v>
+        <v>46331</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
-        <v>46331</v>
+        <v>46361</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
-        <v>46361</v>
+        <v>46385</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
-        <v>46385</v>
+        <v>46401</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
-        <v>46401</v>
+        <v>46382</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
-        <v>46382</v>
+        <v>46328</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
-        <v>46328</v>
+        <v>46312</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D49" t="s">
         <v>16</v>
@@ -1405,55 +1392,55 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
-        <v>46312</v>
+        <v>46265</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
-        <v>46265</v>
+        <v>46288</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C51" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
@@ -1461,337 +1448,326 @@
         <v>46326</v>
       </c>
       <c r="B54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
-        <v>46326</v>
+        <v>46346</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
-        <v>46346</v>
+        <v>46366</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
-        <v>46366</v>
+        <v>46385</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
-        <v>46385</v>
+        <v>46285</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="C58" t="s">
+        <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C59" t="s">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
-      </c>
-      <c r="C60" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
-        <v>46305</v>
+        <v>46315</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
-        <v>46315</v>
+        <v>46326</v>
       </c>
       <c r="B62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
-        <v>46326</v>
+        <v>46277</v>
       </c>
       <c r="B63" t="s">
         <v>80</v>
       </c>
+      <c r="C63" t="s">
+        <v>4</v>
+      </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
-        <v>46277</v>
+        <v>46290</v>
       </c>
       <c r="B64" t="s">
+        <v>81</v>
+      </c>
+      <c r="C64" t="s">
+        <v>113</v>
+      </c>
+      <c r="D64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A65" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C64" t="s">
-        <v>5</v>
-      </c>
-      <c r="D64" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A65" s="2">
-        <v>46290</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="D65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B66" t="s">
         <v>83</v>
       </c>
-      <c r="C65" t="s">
-        <v>115</v>
-      </c>
-      <c r="D65" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A66" s="2">
-        <v>46295</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>84</v>
+      <c r="C66" t="s">
+        <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
-        <v>46275</v>
+        <v>46265</v>
       </c>
       <c r="B67" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C68" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="D68" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C69" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
-        <v>46305</v>
+        <v>46300</v>
       </c>
       <c r="B70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
-        <v>46300</v>
+        <v>46290</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C72" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B73" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C73" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
-      </c>
-      <c r="C74" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D74" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
-        <v>46300</v>
+        <v>46341</v>
       </c>
       <c r="B75" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
-        <v>46341</v>
+        <v>46356</v>
       </c>
       <c r="B76" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
-        <v>46356</v>
+        <v>46351</v>
       </c>
       <c r="B77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
-        <v>46351</v>
+        <v>46326</v>
       </c>
       <c r="B78" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="B79" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D79" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A80" s="2">
-        <v>46295</v>
-      </c>
-      <c r="B80" t="s">
-        <v>116</v>
-      </c>
-      <c r="D80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D22">
-    <sortCondition ref="A2:A22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D21">
+    <sortCondition ref="A2:A21"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="446" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EC73659-2317-417D-AFEC-378FF0008CBD}"/>
+  <xr:revisionPtr revIDLastSave="552" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{851DC382-273E-4216-B7AD-3E0E6EB5C291}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="147">
   <si>
     <t>Date</t>
   </si>
@@ -107,9 +107,6 @@
     <t>Transfer Tower Foundation handover</t>
   </si>
   <si>
-    <t>AHP Stg-1 and Stg-2 Foundation handover</t>
-  </si>
-  <si>
     <t xml:space="preserve">ESP-CR 8.5m structure works completion </t>
   </si>
   <si>
@@ -140,9 +137,6 @@
     <t xml:space="preserve">CER to ESP RHS Foundation completion </t>
   </si>
   <si>
-    <t>Delayed -30.06.26/15.07.26/30.07.26/10.08.26</t>
-  </si>
-  <si>
     <t xml:space="preserve">CER to ESP LHS Foundation completion </t>
   </si>
   <si>
@@ -380,7 +374,106 @@
     <t xml:space="preserve">Eco Hopper erection </t>
   </si>
   <si>
-    <t>Delayed - 30.08.26/15.09.26/25.09.26</t>
+    <t>Delayed - 30.08.26/15.09.26/25.09.26/28.09.26</t>
+  </si>
+  <si>
+    <t>Delayed - 10.09.26/20.09.26/25.09.26</t>
+  </si>
+  <si>
+    <t>Delayed - 25-09-2026</t>
+  </si>
+  <si>
+    <t>AHP Stg-2 Foundation handover</t>
+  </si>
+  <si>
+    <t>Delayed -30.06.26/15.07.26/30.07.26/10.08.26/31.08.26</t>
+  </si>
+  <si>
+    <t>Condenser pit staircase completion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotbox -0M TG side platform completion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotbox -0m Gen side platform completion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C row - TDBP area platform completion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TDBP Deck staircase completion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPH A row sheeting works completion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPH C row sheeting works completion </t>
+  </si>
+  <si>
+    <t>Boiler TG Intercoonection beam works from civil side</t>
+  </si>
+  <si>
+    <t>Electrical - 200 manpower by Shriram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOT, TG ECW- Cable tray completion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FD/PA 3A cable tray completion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boiler LHS Cable tray riser completion </t>
+  </si>
+  <si>
+    <t>Boiler RHS Cable tray riser completion</t>
+  </si>
+  <si>
+    <t>Mot AOP, Centrifuge and MDBP LOP trial</t>
+  </si>
+  <si>
+    <t>Delayed - 20.09.26/27.09.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0DC Board charging </t>
+  </si>
+  <si>
+    <t>3DB-TMCC Charging</t>
+  </si>
+  <si>
+    <t>3DG - DG MCC Charging</t>
+  </si>
+  <si>
+    <t>Mill unloading bay area paving  completion</t>
+  </si>
+  <si>
+    <t>K row drain and approach completion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cable rack foundation/Pull pit/Duct bank for FD/PA 3B </t>
+  </si>
+  <si>
+    <t>Boiler area paving - RHS from PA Fan to APH completion</t>
+  </si>
+  <si>
+    <t>Boiler Unit 1 Passenger lift handover</t>
+  </si>
+  <si>
+    <t>ESP Unit 1 Hoists commissioning</t>
+  </si>
+  <si>
+    <t>Unit 1 ESP-CR lift commissioning</t>
+  </si>
+  <si>
+    <t>Unit 2 Boiler all hoists commissioning completion</t>
+  </si>
+  <si>
+    <t>Unit 2 Boiler MC room lift casting</t>
+  </si>
+  <si>
+    <t>PA Fan 3A casting completion</t>
+  </si>
+  <si>
+    <t>Delayed - 31.08.26/20.09.26</t>
   </si>
 </sst>
 </file>
@@ -746,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -875,7 +968,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -886,10 +979,10 @@
         <v>46295</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -900,10 +993,10 @@
         <v>46290</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -914,10 +1007,10 @@
         <v>46295</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -931,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -942,10 +1035,10 @@
         <v>46295</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -956,7 +1049,7 @@
         <v>46280</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
@@ -973,7 +1066,7 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1039,7 +1132,7 @@
         <v>46254</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
@@ -1053,7 +1146,7 @@
         <v>45991</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -1064,7 +1157,7 @@
         <v>46321</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -1072,10 +1165,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -1086,7 +1182,7 @@
         <v>46402</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
         <v>15</v>
@@ -1097,10 +1193,10 @@
         <v>46265</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -1111,10 +1207,10 @@
         <v>46270</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -1125,10 +1221,10 @@
         <v>46270</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -1139,10 +1235,10 @@
         <v>46275</v>
       </c>
       <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
         <v>40</v>
-      </c>
-      <c r="C30" t="s">
-        <v>42</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -1153,10 +1249,10 @@
         <v>46275</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -1167,10 +1263,10 @@
         <v>46310</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -1181,10 +1277,10 @@
         <v>46285</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -1195,10 +1291,10 @@
         <v>46295</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -1209,10 +1305,10 @@
         <v>46290</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -1223,7 +1319,7 @@
         <v>46254</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
@@ -1237,7 +1333,7 @@
         <v>46272</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
@@ -1251,10 +1347,10 @@
         <v>46285</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -1262,13 +1358,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
@@ -1276,13 +1372,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D40" t="s">
         <v>15</v>
@@ -1290,13 +1386,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
-        <v>46305</v>
+        <v>46315</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D41" t="s">
         <v>15</v>
@@ -1307,7 +1403,7 @@
         <v>46320</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D42" t="s">
         <v>15</v>
@@ -1318,7 +1414,7 @@
         <v>46331</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D43" t="s">
         <v>15</v>
@@ -1329,7 +1425,7 @@
         <v>46361</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D44" t="s">
         <v>15</v>
@@ -1340,7 +1436,7 @@
         <v>46385</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D45" t="s">
         <v>15</v>
@@ -1351,7 +1447,7 @@
         <v>46401</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
         <v>15</v>
@@ -1362,7 +1458,7 @@
         <v>46382</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
@@ -1373,7 +1469,7 @@
         <v>46328</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
@@ -1384,7 +1480,7 @@
         <v>46312</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D49" t="s">
         <v>16</v>
@@ -1395,7 +1491,7 @@
         <v>46265</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
@@ -1409,10 +1505,10 @@
         <v>46288</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D51" t="s">
         <v>15</v>
@@ -1423,10 +1519,10 @@
         <v>46295</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
@@ -1437,7 +1533,7 @@
         <v>46326</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D53" t="s">
         <v>15</v>
@@ -1448,7 +1544,7 @@
         <v>46326</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D54" t="s">
         <v>15</v>
@@ -1459,7 +1555,7 @@
         <v>46346</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
         <v>15</v>
@@ -1470,7 +1566,7 @@
         <v>46366</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D56" t="s">
         <v>15</v>
@@ -1481,7 +1577,7 @@
         <v>46385</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D57" t="s">
         <v>15</v>
@@ -1492,7 +1588,7 @@
         <v>46285</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C58" t="s">
         <v>4</v>
@@ -1506,10 +1602,10 @@
         <v>46295</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C59" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D59" t="s">
         <v>15</v>
@@ -1520,7 +1616,7 @@
         <v>46305</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D60" t="s">
         <v>15</v>
@@ -1531,7 +1627,7 @@
         <v>46315</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D61" t="s">
         <v>15</v>
@@ -1542,7 +1638,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D62" t="s">
         <v>15</v>
@@ -1553,7 +1649,7 @@
         <v>46277</v>
       </c>
       <c r="B63" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C63" t="s">
         <v>4</v>
@@ -1564,13 +1660,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B64" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D64" t="s">
         <v>17</v>
@@ -1578,10 +1674,10 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A65" s="2">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D65" t="s">
         <v>17</v>
@@ -1592,7 +1688,7 @@
         <v>46275</v>
       </c>
       <c r="B66" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C66" t="s">
         <v>4</v>
@@ -1606,7 +1702,7 @@
         <v>46265</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C67" t="s">
         <v>4</v>
@@ -1620,10 +1716,10 @@
         <v>46295</v>
       </c>
       <c r="B68" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C68" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D68" t="s">
         <v>16</v>
@@ -1634,10 +1730,10 @@
         <v>46305</v>
       </c>
       <c r="B69" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D69" t="s">
         <v>16</v>
@@ -1648,10 +1744,10 @@
         <v>46300</v>
       </c>
       <c r="B70" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C70" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
         <v>16</v>
@@ -1662,10 +1758,10 @@
         <v>46290</v>
       </c>
       <c r="B71" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D71" t="s">
         <v>16</v>
@@ -1673,13 +1769,13 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="B72" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C72" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D72" t="s">
         <v>16</v>
@@ -1690,10 +1786,10 @@
         <v>46295</v>
       </c>
       <c r="B73" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D73" t="s">
         <v>16</v>
@@ -1704,7 +1800,7 @@
         <v>46300</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D74" t="s">
         <v>15</v>
@@ -1715,7 +1811,7 @@
         <v>46341</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D75" t="s">
         <v>15</v>
@@ -1726,7 +1822,7 @@
         <v>46356</v>
       </c>
       <c r="B76" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D76" t="s">
         <v>15</v>
@@ -1737,7 +1833,7 @@
         <v>46351</v>
       </c>
       <c r="B77" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
@@ -1748,7 +1844,7 @@
         <v>46326</v>
       </c>
       <c r="B78" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D78" t="s">
         <v>15</v>
@@ -1759,10 +1855,313 @@
         <v>46295</v>
       </c>
       <c r="B79" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D79" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A80" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B80" t="s">
+        <v>118</v>
+      </c>
+      <c r="D80" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A81" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B81" t="s">
+        <v>119</v>
+      </c>
+      <c r="D81" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A82" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B82" t="s">
+        <v>120</v>
+      </c>
+      <c r="D82" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A83" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B83" t="s">
+        <v>121</v>
+      </c>
+      <c r="D83" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A84" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B84" t="s">
+        <v>122</v>
+      </c>
+      <c r="D84" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A85" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B85" t="s">
+        <v>123</v>
+      </c>
+      <c r="D85" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A86" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B86" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A87" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B87" t="s">
+        <v>125</v>
+      </c>
+      <c r="D87" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A88" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B88" t="s">
+        <v>126</v>
+      </c>
+      <c r="D88" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A89" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B89" t="s">
+        <v>127</v>
+      </c>
+      <c r="D89" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A90" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B90" t="s">
+        <v>128</v>
+      </c>
+      <c r="D90" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A91" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B91" t="s">
+        <v>129</v>
+      </c>
+      <c r="D91" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A92" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B92" t="s">
+        <v>130</v>
+      </c>
+      <c r="D92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A93" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B93" t="s">
+        <v>131</v>
+      </c>
+      <c r="C93" t="s">
+        <v>132</v>
+      </c>
+      <c r="D93" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A94" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B94" t="s">
+        <v>133</v>
+      </c>
+      <c r="D94" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A95" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B95" t="s">
+        <v>134</v>
+      </c>
+      <c r="D95" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A96" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B96" t="s">
+        <v>135</v>
+      </c>
+      <c r="D96" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A97" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B97" t="s">
+        <v>136</v>
+      </c>
+      <c r="D97" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A98" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B98" t="s">
+        <v>137</v>
+      </c>
+      <c r="D98" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A99" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B99" t="s">
+        <v>138</v>
+      </c>
+      <c r="D99" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A100" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B100" t="s">
+        <v>139</v>
+      </c>
+      <c r="D100" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A101" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B101" t="s">
+        <v>140</v>
+      </c>
+      <c r="D101" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A102" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B102" t="s">
+        <v>141</v>
+      </c>
+      <c r="D102" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A103" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B103" t="s">
+        <v>142</v>
+      </c>
+      <c r="D103" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A104" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B104" t="s">
+        <v>143</v>
+      </c>
+      <c r="D104" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A105" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B105" t="s">
+        <v>144</v>
+      </c>
+      <c r="D105" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A106" s="2">
+        <v>47390</v>
+      </c>
+      <c r="B106" t="s">
+        <v>145</v>
+      </c>
+      <c r="C106" t="s">
+        <v>146</v>
+      </c>
+      <c r="D106" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="552" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{851DC382-273E-4216-B7AD-3E0E6EB5C291}"/>
+  <xr:revisionPtr revIDLastSave="567" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F569598-AF1F-4B80-8F0C-76215BE035C0}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="145">
   <si>
     <t>Date</t>
   </si>
@@ -140,24 +140,15 @@
     <t xml:space="preserve">CER to ESP LHS Foundation completion </t>
   </si>
   <si>
-    <t>Delayed -30.06.26/15.07.26/30.07.26/14.08.26</t>
-  </si>
-  <si>
     <t xml:space="preserve">CER to Boiler Foundation completion </t>
   </si>
   <si>
-    <t>Delayed -30.06.26/15.07.26/30.07.26/14.08.27</t>
-  </si>
-  <si>
     <t>ESP to ESP Control Room (LHS) – Electromech/RVPR</t>
   </si>
   <si>
     <t>ESP to ESP Control Room (RHS)</t>
   </si>
   <si>
-    <t>Delayed -30.07.26/20.08.26</t>
-  </si>
-  <si>
     <t>FD 3A foundation completion</t>
   </si>
   <si>
@@ -188,9 +179,6 @@
     <t>ACC - Street 3 ATT</t>
   </si>
   <si>
-    <t>Delayed - 30.07.26/14.08.26/31.08.26</t>
-  </si>
-  <si>
     <t>Delayed - R0 - 25.08.26</t>
   </si>
   <si>
@@ -314,18 +302,12 @@
     <t>Delayed - 30.08.26/30.09.26</t>
   </si>
   <si>
-    <t>Delayed -  10.08.26/31.08.26/10.09.26</t>
-  </si>
-  <si>
     <t>Delayed R0 - 25.08.26/15.09.26</t>
   </si>
   <si>
     <t>Delayed - R0 - 15.09.26</t>
   </si>
   <si>
-    <t>Delayed-31.08.26</t>
-  </si>
-  <si>
     <t>Delayed - 20.09.26</t>
   </si>
   <si>
@@ -386,9 +368,6 @@
     <t>AHP Stg-2 Foundation handover</t>
   </si>
   <si>
-    <t>Delayed -30.06.26/15.07.26/30.07.26/10.08.26/31.08.26</t>
-  </si>
-  <si>
     <t>Condenser pit staircase completion</t>
   </si>
   <si>
@@ -474,6 +453,21 @@
   </si>
   <si>
     <t>Delayed - 31.08.26/20.09.26</t>
+  </si>
+  <si>
+    <t>Delayed -30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.10.26</t>
+  </si>
+  <si>
+    <t>Delayed -30.06.26/15.07.26/30.07.26/14.08.26/05.09.26</t>
+  </si>
+  <si>
+    <t>Delayed -30.07.26/20.08.26/10.09.26</t>
+  </si>
+  <si>
+    <t>Delayed -  10.08.26/31.08.26/10.09.26/30.09.26</t>
+  </si>
+  <si>
+    <t>Delayed - 30-09-26</t>
   </si>
 </sst>
 </file>
@@ -979,10 +973,10 @@
         <v>46295</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -996,7 +990,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -1007,10 +1001,10 @@
         <v>46295</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1024,7 +1018,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -1038,7 +1032,7 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -1066,7 +1060,7 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1171,7 +1165,7 @@
         <v>31</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -1190,13 +1184,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
-        <v>46265</v>
+        <v>46305</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -1204,13 +1198,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
-        <v>46270</v>
+        <v>46300</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -1221,10 +1215,10 @@
         <v>46270</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -1232,13 +1226,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
-        <v>46275</v>
+        <v>46310</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -1249,10 +1243,10 @@
         <v>46275</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -1263,10 +1257,10 @@
         <v>46310</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -1274,13 +1268,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -1291,10 +1285,10 @@
         <v>46295</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -1305,10 +1299,10 @@
         <v>46290</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -1319,7 +1313,7 @@
         <v>46254</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
@@ -1333,7 +1327,7 @@
         <v>46272</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
@@ -1347,10 +1341,10 @@
         <v>46285</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -1361,10 +1355,10 @@
         <v>46295</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
@@ -1375,10 +1369,10 @@
         <v>46305</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
         <v>15</v>
@@ -1389,10 +1383,10 @@
         <v>46315</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C41" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
         <v>15</v>
@@ -1403,7 +1397,7 @@
         <v>46320</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
         <v>15</v>
@@ -1414,7 +1408,7 @@
         <v>46331</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D43" t="s">
         <v>15</v>
@@ -1425,7 +1419,7 @@
         <v>46361</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D44" t="s">
         <v>15</v>
@@ -1436,7 +1430,7 @@
         <v>46385</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D45" t="s">
         <v>15</v>
@@ -1447,7 +1441,7 @@
         <v>46401</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D46" t="s">
         <v>15</v>
@@ -1458,7 +1452,7 @@
         <v>46382</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
@@ -1469,7 +1463,7 @@
         <v>46328</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
@@ -1480,7 +1474,7 @@
         <v>46312</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D49" t="s">
         <v>16</v>
@@ -1491,7 +1485,7 @@
         <v>46265</v>
       </c>
       <c r="B50" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
@@ -1502,13 +1496,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B51" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D51" t="s">
         <v>15</v>
@@ -1519,10 +1513,10 @@
         <v>46295</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
@@ -1533,7 +1527,7 @@
         <v>46326</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D53" t="s">
         <v>15</v>
@@ -1544,7 +1538,7 @@
         <v>46326</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D54" t="s">
         <v>15</v>
@@ -1555,7 +1549,7 @@
         <v>46346</v>
       </c>
       <c r="B55" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D55" t="s">
         <v>15</v>
@@ -1566,7 +1560,7 @@
         <v>46366</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D56" t="s">
         <v>15</v>
@@ -1577,7 +1571,7 @@
         <v>46385</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D57" t="s">
         <v>15</v>
@@ -1588,7 +1582,7 @@
         <v>46285</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
         <v>4</v>
@@ -1599,13 +1593,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C59" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D59" t="s">
         <v>15</v>
@@ -1616,7 +1610,10 @@
         <v>46305</v>
       </c>
       <c r="B60" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C60" t="s">
+        <v>144</v>
       </c>
       <c r="D60" t="s">
         <v>15</v>
@@ -1627,7 +1624,7 @@
         <v>46315</v>
       </c>
       <c r="B61" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D61" t="s">
         <v>15</v>
@@ -1638,7 +1635,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D62" t="s">
         <v>15</v>
@@ -1649,7 +1646,7 @@
         <v>46277</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C63" t="s">
         <v>4</v>
@@ -1663,10 +1660,10 @@
         <v>46295</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C64" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D64" t="s">
         <v>17</v>
@@ -1677,7 +1674,7 @@
         <v>46301</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D65" t="s">
         <v>17</v>
@@ -1688,7 +1685,7 @@
         <v>46275</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C66" t="s">
         <v>4</v>
@@ -1702,7 +1699,7 @@
         <v>46265</v>
       </c>
       <c r="B67" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C67" t="s">
         <v>4</v>
@@ -1716,10 +1713,10 @@
         <v>46295</v>
       </c>
       <c r="B68" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D68" t="s">
         <v>16</v>
@@ -1730,10 +1727,10 @@
         <v>46305</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C69" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D69" t="s">
         <v>16</v>
@@ -1744,10 +1741,10 @@
         <v>46300</v>
       </c>
       <c r="B70" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D70" t="s">
         <v>16</v>
@@ -1755,13 +1752,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B71" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C71" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D71" t="s">
         <v>16</v>
@@ -1772,10 +1769,10 @@
         <v>46300</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C72" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D72" t="s">
         <v>16</v>
@@ -1786,10 +1783,10 @@
         <v>46295</v>
       </c>
       <c r="B73" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C73" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D73" t="s">
         <v>16</v>
@@ -1800,7 +1797,7 @@
         <v>46300</v>
       </c>
       <c r="B74" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D74" t="s">
         <v>15</v>
@@ -1811,7 +1808,7 @@
         <v>46341</v>
       </c>
       <c r="B75" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D75" t="s">
         <v>15</v>
@@ -1822,7 +1819,7 @@
         <v>46356</v>
       </c>
       <c r="B76" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D76" t="s">
         <v>15</v>
@@ -1833,7 +1830,7 @@
         <v>46351</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
@@ -1844,7 +1841,7 @@
         <v>46326</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D78" t="s">
         <v>15</v>
@@ -1855,7 +1852,7 @@
         <v>46295</v>
       </c>
       <c r="B79" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D79" t="s">
         <v>15</v>
@@ -1866,7 +1863,7 @@
         <v>46317</v>
       </c>
       <c r="B80" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D80" t="s">
         <v>17</v>
@@ -1877,7 +1874,7 @@
         <v>46302</v>
       </c>
       <c r="B81" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D81" t="s">
         <v>17</v>
@@ -1888,7 +1885,7 @@
         <v>46295</v>
       </c>
       <c r="B82" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D82" t="s">
         <v>17</v>
@@ -1899,7 +1896,7 @@
         <v>46315</v>
       </c>
       <c r="B83" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D83" t="s">
         <v>17</v>
@@ -1910,7 +1907,7 @@
         <v>46302</v>
       </c>
       <c r="B84" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D84" t="s">
         <v>17</v>
@@ -1921,7 +1918,7 @@
         <v>46310</v>
       </c>
       <c r="B85" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D85" t="s">
         <v>17</v>
@@ -1932,7 +1929,7 @@
         <v>46320</v>
       </c>
       <c r="B86" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D86" t="s">
         <v>17</v>
@@ -1943,7 +1940,7 @@
         <v>46323</v>
       </c>
       <c r="B87" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D87" t="s">
         <v>17</v>
@@ -1954,7 +1951,7 @@
         <v>46295</v>
       </c>
       <c r="B88" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D88" t="s">
         <v>17</v>
@@ -1965,7 +1962,7 @@
         <v>46305</v>
       </c>
       <c r="B89" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D89" t="s">
         <v>17</v>
@@ -1976,7 +1973,7 @@
         <v>46295</v>
       </c>
       <c r="B90" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D90" t="s">
         <v>16</v>
@@ -1987,7 +1984,7 @@
         <v>46305</v>
       </c>
       <c r="B91" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D91" t="s">
         <v>16</v>
@@ -1998,7 +1995,7 @@
         <v>46320</v>
       </c>
       <c r="B92" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D92" t="s">
         <v>16</v>
@@ -2009,10 +2006,10 @@
         <v>46297</v>
       </c>
       <c r="B93" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C93" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D93" t="s">
         <v>16</v>
@@ -2023,7 +2020,7 @@
         <v>46310</v>
       </c>
       <c r="B94" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D94" t="s">
         <v>16</v>
@@ -2034,7 +2031,7 @@
         <v>46315</v>
       </c>
       <c r="B95" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D95" t="s">
         <v>16</v>
@@ -2045,7 +2042,7 @@
         <v>46320</v>
       </c>
       <c r="B96" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D96" t="s">
         <v>16</v>
@@ -2056,7 +2053,7 @@
         <v>46300</v>
       </c>
       <c r="B97" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D97" t="s">
         <v>17</v>
@@ -2067,7 +2064,7 @@
         <v>46305</v>
       </c>
       <c r="B98" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D98" t="s">
         <v>17</v>
@@ -2078,7 +2075,7 @@
         <v>46305</v>
       </c>
       <c r="B99" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D99" t="s">
         <v>17</v>
@@ -2089,7 +2086,7 @@
         <v>46315</v>
       </c>
       <c r="B100" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D100" t="s">
         <v>17</v>
@@ -2100,7 +2097,7 @@
         <v>46290</v>
       </c>
       <c r="B101" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D101" t="s">
         <v>15</v>
@@ -2111,7 +2108,7 @@
         <v>46305</v>
       </c>
       <c r="B102" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D102" t="s">
         <v>15</v>
@@ -2122,7 +2119,7 @@
         <v>46295</v>
       </c>
       <c r="B103" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D103" t="s">
         <v>15</v>
@@ -2133,7 +2130,7 @@
         <v>46326</v>
       </c>
       <c r="B104" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D104" t="s">
         <v>15</v>
@@ -2144,7 +2141,7 @@
         <v>46295</v>
       </c>
       <c r="B105" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
         <v>17</v>
@@ -2155,10 +2152,10 @@
         <v>47390</v>
       </c>
       <c r="B106" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C106" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D106" t="s">
         <v>17</v>

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="567" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F569598-AF1F-4B80-8F0C-76215BE035C0}"/>
+  <xr:revisionPtr revIDLastSave="635" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6886C8E1-0699-43A6-A1BD-4E4586776518}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="149">
   <si>
     <t>Date</t>
   </si>
@@ -116,9 +116,6 @@
     <t>Start of LP Turbine erection after hotbox completion</t>
   </si>
   <si>
-    <t>Delayed R0 - 15-09-26</t>
-  </si>
-  <si>
     <t>Hotbox bottom plate erection</t>
   </si>
   <si>
@@ -263,9 +260,6 @@
     <t>BMCC to CER Cantilever cable gallery-start</t>
   </si>
   <si>
-    <t>BMCC to CER Cantilever cable gallery- completion</t>
-  </si>
-  <si>
     <t>C row balance cable gallery handover</t>
   </si>
   <si>
@@ -275,9 +269,6 @@
     <t>0BE Board charging</t>
   </si>
   <si>
-    <t>3CA Board charging</t>
-  </si>
-  <si>
     <t>3BA Board charging</t>
   </si>
   <si>
@@ -290,9 +281,6 @@
     <t>UAT-3A charging</t>
   </si>
   <si>
-    <t>Delayed - 23/09/26</t>
-  </si>
-  <si>
     <t>Delayed R0 - 05-09-26</t>
   </si>
   <si>
@@ -314,18 +302,9 @@
     <t>Delayed - 30.09.26</t>
   </si>
   <si>
-    <t>Delayed - 04.09.26/10.09.26</t>
-  </si>
-  <si>
     <t>Delayed - 14-09-26</t>
   </si>
   <si>
-    <t>Delayed - 15.09.26</t>
-  </si>
-  <si>
-    <t>Delayed - 26.09.26</t>
-  </si>
-  <si>
     <t>Delayed - 29.09.26</t>
   </si>
   <si>
@@ -359,9 +338,6 @@
     <t>Delayed - 30.08.26/15.09.26/25.09.26/28.09.26</t>
   </si>
   <si>
-    <t>Delayed - 10.09.26/20.09.26/25.09.26</t>
-  </si>
-  <si>
     <t>Delayed - 25-09-2026</t>
   </si>
   <si>
@@ -389,12 +365,6 @@
     <t xml:space="preserve">MPH C row sheeting works completion </t>
   </si>
   <si>
-    <t>Boiler TG Intercoonection beam works from civil side</t>
-  </si>
-  <si>
-    <t>Electrical - 200 manpower by Shriram</t>
-  </si>
-  <si>
     <t xml:space="preserve">MOT, TG ECW- Cable tray completion </t>
   </si>
   <si>
@@ -468,13 +438,55 @@
   </si>
   <si>
     <t>Delayed - 30-09-26</t>
+  </si>
+  <si>
+    <t>Delayed - 15.09.26/30.09.26</t>
+  </si>
+  <si>
+    <t>Delayed - 26.09.26/10.10.26</t>
+  </si>
+  <si>
+    <t>Delayed - 25.10.26</t>
+  </si>
+  <si>
+    <t>TG, SG ECW pps motor no load trial</t>
+  </si>
+  <si>
+    <t>FD Fan-B Main Motor Trial Run</t>
+  </si>
+  <si>
+    <t>3.3KV - 3CA Board charging</t>
+  </si>
+  <si>
+    <t>TG ECW Lines readiness for HT</t>
+  </si>
+  <si>
+    <t>Deaerator - HT</t>
+  </si>
+  <si>
+    <t>SG ECW lines readiness for HT</t>
+  </si>
+  <si>
+    <t>Delayed - 05.10.26</t>
+  </si>
+  <si>
+    <t>Electrical - 250 manpower by Shriram</t>
+  </si>
+  <si>
+    <t>Delayed - 23.09.26/30.09.26</t>
+  </si>
+  <si>
+    <t>Boiler TG Interconnection beam works from civil side</t>
+  </si>
+  <si>
+    <t>Delayed R0 - 15-09-26/15-10-26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,8 +512,14 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF242424"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -513,8 +531,14 @@
         <fgColor rgb="FF005A9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -522,15 +546,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -956,13 +1017,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
-        <v>46310</v>
+        <v>46341</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -973,10 +1034,10 @@
         <v>46295</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -990,7 +1051,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -1001,10 +1062,10 @@
         <v>46295</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1018,7 +1079,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -1032,7 +1093,7 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -1060,7 +1121,7 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1126,7 +1187,7 @@
         <v>46254</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
@@ -1137,10 +1198,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
-        <v>45991</v>
+        <v>46356</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -1151,7 +1212,7 @@
         <v>46321</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -1162,10 +1223,10 @@
         <v>46295</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -1176,7 +1237,7 @@
         <v>46402</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
         <v>15</v>
@@ -1187,10 +1248,10 @@
         <v>46305</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -1198,13 +1259,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
-        <v>46300</v>
+        <v>46320</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -1215,7 +1276,7 @@
         <v>46270</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
@@ -1229,10 +1290,10 @@
         <v>46310</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -1243,7 +1304,7 @@
         <v>46275</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
@@ -1257,10 +1318,10 @@
         <v>46310</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -1271,10 +1332,10 @@
         <v>46295</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -1285,10 +1346,10 @@
         <v>46295</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -1299,10 +1360,10 @@
         <v>46290</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -1313,7 +1374,7 @@
         <v>46254</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
@@ -1327,7 +1388,7 @@
         <v>46272</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
@@ -1341,7 +1402,7 @@
         <v>46285</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
@@ -1352,13 +1413,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
@@ -1366,13 +1427,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
         <v>15</v>
@@ -1380,13 +1441,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
-        <v>46315</v>
+        <v>46320</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
         <v>15</v>
@@ -1394,10 +1455,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
-        <v>46320</v>
+        <v>46331</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
         <v>15</v>
@@ -1405,10 +1466,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
-        <v>46331</v>
+        <v>46341</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
         <v>15</v>
@@ -1419,7 +1480,7 @@
         <v>46361</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D44" t="s">
         <v>15</v>
@@ -1430,7 +1491,7 @@
         <v>46385</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D45" t="s">
         <v>15</v>
@@ -1441,7 +1502,7 @@
         <v>46401</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D46" t="s">
         <v>15</v>
@@ -1452,7 +1513,7 @@
         <v>46382</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
@@ -1463,7 +1524,7 @@
         <v>46328</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
@@ -1474,7 +1535,7 @@
         <v>46312</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D49" t="s">
         <v>16</v>
@@ -1485,7 +1546,7 @@
         <v>46265</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
@@ -1499,10 +1560,10 @@
         <v>46290</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="D51" t="s">
         <v>15</v>
@@ -1513,10 +1574,10 @@
         <v>46295</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
@@ -1527,7 +1588,7 @@
         <v>46326</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
         <v>15</v>
@@ -1538,7 +1599,7 @@
         <v>46326</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D54" t="s">
         <v>15</v>
@@ -1549,7 +1610,7 @@
         <v>46346</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D55" t="s">
         <v>15</v>
@@ -1560,7 +1621,7 @@
         <v>46366</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D56" t="s">
         <v>15</v>
@@ -1571,7 +1632,7 @@
         <v>46385</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D57" t="s">
         <v>15</v>
@@ -1582,7 +1643,7 @@
         <v>46285</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" t="s">
         <v>4</v>
@@ -1596,10 +1657,10 @@
         <v>46305</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D59" t="s">
         <v>15</v>
@@ -1610,10 +1671,10 @@
         <v>46305</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C60" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D60" t="s">
         <v>15</v>
@@ -1624,7 +1685,7 @@
         <v>46315</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D61" t="s">
         <v>15</v>
@@ -1635,7 +1696,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D62" t="s">
         <v>15</v>
@@ -1646,7 +1707,7 @@
         <v>46277</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C63" t="s">
         <v>4</v>
@@ -1660,21 +1721,24 @@
         <v>46295</v>
       </c>
       <c r="B64" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" t="s">
+        <v>98</v>
+      </c>
+      <c r="D64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B65" t="s">
         <v>75</v>
       </c>
-      <c r="C64" t="s">
-        <v>105</v>
-      </c>
-      <c r="D64" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A65" s="2">
-        <v>46301</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>76</v>
+      <c r="C65" t="s">
+        <v>4</v>
       </c>
       <c r="D65" t="s">
         <v>17</v>
@@ -1682,10 +1746,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
-        <v>46275</v>
+        <v>46265</v>
       </c>
       <c r="B66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C66" t="s">
         <v>4</v>
@@ -1696,27 +1760,27 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
-        <v>46265</v>
+        <v>46320</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="D67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
-        <v>46295</v>
+        <v>46315</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="C68" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="D68" t="s">
         <v>16</v>
@@ -1724,13 +1788,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
-        <v>46305</v>
+        <v>46300</v>
       </c>
       <c r="B69" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D69" t="s">
         <v>16</v>
@@ -1738,10 +1802,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="B70" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C70" t="s">
         <v>97</v>
@@ -1752,13 +1816,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="B71" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D71" t="s">
         <v>16</v>
@@ -1766,13 +1830,13 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
-        <v>46300</v>
+        <v>46310</v>
       </c>
       <c r="B72" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="D72" t="s">
         <v>16</v>
@@ -1780,24 +1844,24 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
-        <v>46295</v>
+        <v>46310</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C73" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
-        <v>46300</v>
+        <v>46341</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D74" t="s">
         <v>15</v>
@@ -1805,10 +1869,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
-        <v>46341</v>
+        <v>46356</v>
       </c>
       <c r="B75" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D75" t="s">
         <v>15</v>
@@ -1816,10 +1880,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
-        <v>46356</v>
+        <v>46351</v>
       </c>
       <c r="B76" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D76" t="s">
         <v>15</v>
@@ -1827,10 +1891,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
-        <v>46351</v>
+        <v>46326</v>
       </c>
       <c r="B77" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
@@ -1838,10 +1902,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
-        <v>46326</v>
+        <v>46305</v>
       </c>
       <c r="B78" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="C78" t="s">
+        <v>88</v>
       </c>
       <c r="D78" t="s">
         <v>15</v>
@@ -1849,21 +1916,21 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
-        <v>46295</v>
+        <v>46317</v>
       </c>
       <c r="B79" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D79" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
-        <v>46317</v>
+        <v>46302</v>
       </c>
       <c r="B80" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D80" t="s">
         <v>17</v>
@@ -1871,10 +1938,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="B81" t="s">
-        <v>112</v>
+        <v>105</v>
+      </c>
+      <c r="C81" t="s">
+        <v>4</v>
       </c>
       <c r="D81" t="s">
         <v>17</v>
@@ -1882,10 +1952,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
-        <v>46295</v>
+        <v>46315</v>
       </c>
       <c r="B82" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D82" t="s">
         <v>17</v>
@@ -1893,10 +1963,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
-        <v>46315</v>
+        <v>46302</v>
       </c>
       <c r="B83" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D83" t="s">
         <v>17</v>
@@ -1904,10 +1974,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
-        <v>46302</v>
+        <v>46310</v>
       </c>
       <c r="B84" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D84" t="s">
         <v>17</v>
@@ -1915,10 +1985,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
-        <v>46310</v>
+        <v>46320</v>
       </c>
       <c r="B85" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D85" t="s">
         <v>17</v>
@@ -1926,10 +1996,13 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="B86" t="s">
-        <v>117</v>
+        <v>147</v>
+      </c>
+      <c r="C86" t="s">
+        <v>4</v>
       </c>
       <c r="D86" t="s">
         <v>17</v>
@@ -1937,43 +2010,43 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
-        <v>46323</v>
+        <v>46300</v>
       </c>
       <c r="B87" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="D87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="B88" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
-        <v>46305</v>
+        <v>46295</v>
       </c>
       <c r="B89" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="B90" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D90" t="s">
         <v>16</v>
@@ -1981,10 +2054,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
-        <v>46305</v>
+        <v>46320</v>
       </c>
       <c r="B91" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D91" t="s">
         <v>16</v>
@@ -1992,10 +2065,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
-        <v>46320</v>
+        <v>46301</v>
       </c>
       <c r="B92" t="s">
-        <v>123</v>
+        <v>114</v>
+      </c>
+      <c r="C92" t="s">
+        <v>115</v>
       </c>
       <c r="D92" t="s">
         <v>16</v>
@@ -2003,13 +2079,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
-        <v>46297</v>
+        <v>46310</v>
       </c>
       <c r="B93" t="s">
-        <v>124</v>
-      </c>
-      <c r="C93" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D93" t="s">
         <v>16</v>
@@ -2017,10 +2090,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
-        <v>46310</v>
+        <v>46320</v>
       </c>
       <c r="B94" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D94" t="s">
         <v>16</v>
@@ -2028,10 +2101,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
-        <v>46315</v>
+        <v>46331</v>
       </c>
       <c r="B95" t="s">
-        <v>127</v>
+        <v>118</v>
+      </c>
+      <c r="C95" t="s">
+        <v>137</v>
       </c>
       <c r="D95" t="s">
         <v>16</v>
@@ -2039,127 +2115,181 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
-        <v>46320</v>
+        <v>46300</v>
       </c>
       <c r="B96" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
-        <v>46300</v>
+        <v>46305</v>
       </c>
       <c r="B97" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D97" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>46305</v>
       </c>
       <c r="B98" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D98" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B99" t="s">
+        <v>122</v>
+      </c>
+      <c r="D99" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A100" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B100" t="s">
+        <v>123</v>
+      </c>
+      <c r="D100" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A101" s="2">
         <v>46305</v>
       </c>
-      <c r="B99" t="s">
-        <v>131</v>
-      </c>
-      <c r="D99" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A100" s="2">
-        <v>46315</v>
-      </c>
-      <c r="B100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D100" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A101" s="2">
-        <v>46290</v>
-      </c>
       <c r="B101" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
-        <v>46305</v>
+        <v>46295</v>
       </c>
       <c r="B102" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D102" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B103" t="s">
+        <v>126</v>
+      </c>
+      <c r="D103" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A104" s="2">
         <v>46295</v>
       </c>
-      <c r="B103" t="s">
-        <v>135</v>
-      </c>
-      <c r="D103" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A104" s="2">
-        <v>46326</v>
-      </c>
       <c r="B104" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D104" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
-        <v>46295</v>
+        <v>47390</v>
       </c>
       <c r="B105" t="s">
-        <v>137</v>
+        <v>128</v>
+      </c>
+      <c r="C105" t="s">
+        <v>129</v>
       </c>
       <c r="D105" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
-        <v>47390</v>
+        <v>46320</v>
       </c>
       <c r="B106" t="s">
         <v>138</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A107" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B107" t="s">
         <v>139</v>
       </c>
-      <c r="D106" t="s">
-        <v>17</v>
-      </c>
+      <c r="D107" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A108" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C108" s="5"/>
+      <c r="D108" t="s">
+        <v>15</v>
+      </c>
+      <c r="E108" s="6"/>
+      <c r="F108" s="7"/>
+      <c r="G108" s="4"/>
+    </row>
+    <row r="109" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A109" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D109" t="s">
+        <v>15</v>
+      </c>
+      <c r="E109" s="8"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="7"/>
+    </row>
+    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A110" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D110" t="s">
+        <v>15</v>
+      </c>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="7"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D21">

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="635" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6886C8E1-0699-43A6-A1BD-4E4586776518}"/>
+  <xr:revisionPtr revIDLastSave="683" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91099F73-4F53-4DB2-9B39-796944B44BC1}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="158">
   <si>
     <t>Date</t>
   </si>
@@ -179,9 +179,6 @@
     <t>Delayed - R0 - 25.08.26</t>
   </si>
   <si>
-    <t>Delayed R0 - 30.08.26</t>
-  </si>
-  <si>
     <t>ACC - Street 4 ATT</t>
   </si>
   <si>
@@ -203,9 +200,6 @@
     <t>Delayed R0 - 31-08-26</t>
   </si>
   <si>
-    <t>Delayed R0 - 31-10-26</t>
-  </si>
-  <si>
     <t>MDBP Trial in RC</t>
   </si>
   <si>
@@ -320,9 +314,6 @@
     <t>BFD/BFR/BFS Hydro Test</t>
   </si>
   <si>
-    <t>Delayed - 30.08.26/10.09.26/20.09.26</t>
-  </si>
-  <si>
     <t>Delayed - 10.09.26/20.09.26</t>
   </si>
   <si>
@@ -338,9 +329,6 @@
     <t>Delayed - 30.08.26/15.09.26/25.09.26/28.09.26</t>
   </si>
   <si>
-    <t>Delayed - 25-09-2026</t>
-  </si>
-  <si>
     <t>AHP Stg-2 Foundation handover</t>
   </si>
   <si>
@@ -434,27 +422,57 @@
     <t>Delayed -30.07.26/20.08.26/10.09.26</t>
   </si>
   <si>
-    <t>Delayed -  10.08.26/31.08.26/10.09.26/30.09.26</t>
-  </si>
-  <si>
     <t>Delayed - 30-09-26</t>
   </si>
   <si>
     <t>Delayed - 15.09.26/30.09.26</t>
   </si>
   <si>
+    <t>Delayed - 25.10.26</t>
+  </si>
+  <si>
+    <t>Delayed - 05.11.26</t>
+  </si>
+  <si>
+    <t>Delayed -17.10.26</t>
+  </si>
+  <si>
+    <t>Delayed -31.10.26</t>
+  </si>
+  <si>
+    <t>ID Fan motor trial</t>
+  </si>
+  <si>
+    <t>Delayed -15.11.26</t>
+  </si>
+  <si>
+    <t>Delayed -30.11.26</t>
+  </si>
+  <si>
+    <t>Delayed -25.11.26</t>
+  </si>
+  <si>
+    <t>TG Barring</t>
+  </si>
+  <si>
+    <t>Delayed - 15.11.26</t>
+  </si>
+  <si>
+    <t>Delayed R0 - 31.10.26,18.11.26</t>
+  </si>
+  <si>
+    <t>Delayed - 15.12.26</t>
+  </si>
+  <si>
+    <t>Delayed - 07.02.27</t>
+  </si>
+  <si>
+    <t>Delayed - 25.02.27</t>
+  </si>
+  <si>
     <t>Delayed - 26.09.26/10.10.26</t>
   </si>
   <si>
-    <t>Delayed - 25.10.26</t>
-  </si>
-  <si>
-    <t>TG, SG ECW pps motor no load trial</t>
-  </si>
-  <si>
-    <t>FD Fan-B Main Motor Trial Run</t>
-  </si>
-  <si>
     <t>3.3KV - 3CA Board charging</t>
   </si>
   <si>
@@ -480,6 +498,15 @@
   </si>
   <si>
     <t>Delayed R0 - 15-09-26/15-10-26</t>
+  </si>
+  <si>
+    <t>Delayed - 30.11.26</t>
+  </si>
+  <si>
+    <t>Delayed - 26.10.26</t>
+  </si>
+  <si>
+    <t>Delayed R0 - 30.08.26/30.09.26</t>
   </si>
 </sst>
 </file>
@@ -499,6 +526,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -574,12 +602,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -607,6 +634,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -895,15 +926,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G110"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -917,7 +948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46259</v>
       </c>
@@ -931,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46237</v>
       </c>
@@ -945,7 +976,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46244</v>
       </c>
@@ -959,7 +990,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46251</v>
       </c>
@@ -973,7 +1004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46280</v>
       </c>
@@ -987,7 +1018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46269</v>
       </c>
@@ -1001,7 +1032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46251</v>
       </c>
@@ -1015,7 +1046,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46341</v>
       </c>
@@ -1023,27 +1054,27 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46295</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46290</v>
       </c>
@@ -1057,21 +1088,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>46295</v>
+        <v>46305</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46356</v>
       </c>
@@ -1079,13 +1110,13 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>46295</v>
       </c>
@@ -1093,13 +1124,13 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>46280</v>
       </c>
@@ -1113,65 +1144,77 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46344</v>
+        <v>46366</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46341</v>
+        <v>46381</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
+      <c r="C17" t="s">
+        <v>140</v>
+      </c>
       <c r="D17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46381</v>
+        <v>46402</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
       </c>
+      <c r="C18" t="s">
+        <v>142</v>
+      </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46425</v>
+        <v>46428</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
+      <c r="C19" t="s">
+        <v>143</v>
+      </c>
       <c r="D19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46443</v>
+        <v>46456</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
+      <c r="C20" t="s">
+        <v>144</v>
+      </c>
       <c r="D20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46461</v>
       </c>
@@ -1182,7 +1225,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46254</v>
       </c>
@@ -1196,43 +1239,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46356</v>
+        <v>46371</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
+      <c r="C23" t="s">
+        <v>155</v>
+      </c>
       <c r="D23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>46321</v>
+        <v>46336</v>
       </c>
       <c r="B24" t="s">
         <v>29</v>
       </c>
+      <c r="C24" t="s">
+        <v>156</v>
+      </c>
       <c r="D24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="B25" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>46402</v>
       </c>
@@ -1243,7 +1292,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>46305</v>
       </c>
@@ -1251,13 +1300,13 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>46320</v>
       </c>
@@ -1265,13 +1314,13 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>46270</v>
       </c>
@@ -1285,7 +1334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>46310</v>
       </c>
@@ -1293,13 +1342,13 @@
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>46275</v>
       </c>
@@ -1313,7 +1362,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>46310</v>
       </c>
@@ -1321,27 +1370,27 @@
         <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="B33" t="s">
         <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>46295</v>
       </c>
@@ -1349,13 +1398,13 @@
         <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>46290</v>
       </c>
@@ -1363,13 +1412,13 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>46254</v>
       </c>
@@ -1383,7 +1432,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>46272</v>
       </c>
@@ -1397,7 +1446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>46285</v>
       </c>
@@ -1411,7 +1460,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>46300</v>
       </c>
@@ -1425,7 +1474,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>46310</v>
       </c>
@@ -1433,13 +1482,13 @@
         <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>46320</v>
       </c>
@@ -1447,106 +1496,115 @@
         <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D41" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>46331</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>131</v>
       </c>
       <c r="D42" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>46341</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="C43" t="s">
+        <v>132</v>
       </c>
       <c r="D43" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>46361</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>46385</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D45" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46401</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D46" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46382</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>46328</v>
+        <v>46371</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>46312</v>
+        <v>46320</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="C49" t="s">
+        <v>133</v>
       </c>
       <c r="D49" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>46265</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
@@ -1555,12 +1613,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>46290</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C51" t="s">
         <v>4</v>
@@ -1569,81 +1627,81 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>46295</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>46326</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D53" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>46326</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D54" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>46346</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D55" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>46366</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D56" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>46385</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D57" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>46285</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C58" t="s">
         <v>4</v>
@@ -1652,62 +1710,62 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>46305</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C59" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D59" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>46305</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D60" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>46315</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D61" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>46326</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D62" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>46277</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C63" t="s">
         <v>4</v>
@@ -1716,26 +1774,26 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>46295</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D64" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>46275</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C65" t="s">
         <v>4</v>
@@ -1744,12 +1802,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>46265</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
         <v>4</v>
@@ -1758,190 +1816,202 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>46320</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D67" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>46315</v>
       </c>
       <c r="B68" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C68" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D68" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>46300</v>
       </c>
       <c r="B69" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D69" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>46295</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D70" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>46303</v>
       </c>
       <c r="B71" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D71" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>46310</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D72" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>46310</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C73" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D73" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
+        <v>46371</v>
+      </c>
+      <c r="B74" t="s">
+        <v>89</v>
+      </c>
+      <c r="C74" t="s">
+        <v>136</v>
+      </c>
+      <c r="D74" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>46376</v>
+      </c>
+      <c r="B75" t="s">
+        <v>90</v>
+      </c>
+      <c r="C75" t="s">
+        <v>137</v>
+      </c>
+      <c r="D75" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>46376</v>
+      </c>
+      <c r="B76" t="s">
+        <v>91</v>
+      </c>
+      <c r="C76" t="s">
+        <v>138</v>
+      </c>
+      <c r="D76" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
         <v>46341</v>
       </c>
-      <c r="B74" t="s">
-        <v>91</v>
-      </c>
-      <c r="D74" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="2">
-        <v>46356</v>
-      </c>
-      <c r="B75" t="s">
+      <c r="B77" t="s">
         <v>92</v>
       </c>
-      <c r="D75" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A76" s="2">
-        <v>46351</v>
-      </c>
-      <c r="B76" t="s">
-        <v>93</v>
-      </c>
-      <c r="D76" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A77" s="2">
-        <v>46326</v>
-      </c>
-      <c r="B77" t="s">
-        <v>94</v>
+      <c r="C77" t="s">
+        <v>134</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>46305</v>
       </c>
       <c r="B78" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C78" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D78" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>46317</v>
       </c>
       <c r="B79" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D79" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>46302</v>
       </c>
       <c r="B80" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D80" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>46295</v>
       </c>
       <c r="B81" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C81" t="s">
         <v>4</v>
@@ -1950,56 +2020,56 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>46315</v>
       </c>
       <c r="B82" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D82" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>46302</v>
       </c>
       <c r="B83" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D83" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>46310</v>
       </c>
       <c r="B84" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D84" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>46320</v>
       </c>
       <c r="B85" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D85" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>46323</v>
       </c>
       <c r="B86" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C86" t="s">
         <v>4</v>
@@ -2008,238 +2078,238 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>46300</v>
       </c>
       <c r="B87" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D87" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>46305</v>
       </c>
       <c r="B88" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D88" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>46295</v>
       </c>
       <c r="B89" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D89" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>46305</v>
       </c>
       <c r="B90" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D90" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>46320</v>
       </c>
       <c r="B91" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D91" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>46301</v>
       </c>
       <c r="B92" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C92" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D92" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>46310</v>
       </c>
       <c r="B93" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D93" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>46320</v>
       </c>
       <c r="B94" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D94" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>46331</v>
       </c>
       <c r="B95" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C95" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D95" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>46300</v>
       </c>
       <c r="B96" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D96" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>46305</v>
       </c>
       <c r="B97" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D97" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>46305</v>
       </c>
       <c r="B98" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D98" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>46315</v>
       </c>
       <c r="B99" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D99" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>46290</v>
       </c>
       <c r="B100" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D100" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>46305</v>
       </c>
       <c r="B101" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D101" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>46295</v>
       </c>
       <c r="B102" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D102" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>46326</v>
       </c>
       <c r="B103" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D103" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>46295</v>
       </c>
       <c r="B104" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D104" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>47390</v>
       </c>
       <c r="B105" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D105" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>46320</v>
+        <v>46356</v>
       </c>
       <c r="B106" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D106" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
-        <v>46325</v>
+        <v>46370</v>
       </c>
       <c r="B107" t="s">
         <v>139</v>
@@ -2248,48 +2318,47 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>46315</v>
       </c>
-      <c r="B108" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C108" s="5"/>
+      <c r="B108" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C108" s="4"/>
       <c r="D108" t="s">
         <v>15</v>
       </c>
-      <c r="E108" s="6"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="4"/>
-    </row>
-    <row r="109" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="E108" s="5"/>
+      <c r="F108" s="6"/>
+    </row>
+    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>46310</v>
       </c>
-      <c r="B109" s="5" t="s">
-        <v>143</v>
+      <c r="B109" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
       </c>
-      <c r="E109" s="8"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="7"/>
-    </row>
-    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="E109" s="7"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="6"/>
+    </row>
+    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>46320</v>
       </c>
-      <c r="B110" s="5" t="s">
-        <v>141</v>
+      <c r="B110" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="D110" t="s">
         <v>15</v>
       </c>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="7"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="6"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D21">

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="683" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91099F73-4F53-4DB2-9B39-796944B44BC1}"/>
+  <xr:revisionPtr revIDLastSave="689" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78DABA6C-131C-40EB-830F-A82F9A3BCF73}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="157">
   <si>
     <t>Date</t>
   </si>
@@ -408,9 +408,6 @@
   </si>
   <si>
     <t>PA Fan 3A casting completion</t>
-  </si>
-  <si>
-    <t>Delayed - 31.08.26/20.09.26</t>
   </si>
   <si>
     <t>Delayed -30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.10.26</t>
@@ -634,10 +631,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -926,15 +919,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G110"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -948,7 +941,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>46259</v>
       </c>
@@ -962,7 +955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>46237</v>
       </c>
@@ -976,7 +969,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>46244</v>
       </c>
@@ -990,7 +983,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>46251</v>
       </c>
@@ -1004,7 +997,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>46280</v>
       </c>
@@ -1018,7 +1011,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>46269</v>
       </c>
@@ -1032,7 +1025,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>46251</v>
       </c>
@@ -1046,7 +1039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>46341</v>
       </c>
@@ -1054,13 +1047,13 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>46295</v>
       </c>
@@ -1074,7 +1067,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>46290</v>
       </c>
@@ -1088,7 +1081,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>46305</v>
       </c>
@@ -1096,13 +1089,13 @@
         <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>46356</v>
       </c>
@@ -1116,7 +1109,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>46295</v>
       </c>
@@ -1130,7 +1123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>46280</v>
       </c>
@@ -1144,7 +1137,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>46366</v>
       </c>
@@ -1152,13 +1145,13 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>46381</v>
       </c>
@@ -1166,13 +1159,13 @@
         <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>46402</v>
       </c>
@@ -1180,27 +1173,27 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
-        <v>46428</v>
+        <v>46444</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>46456</v>
       </c>
@@ -1208,13 +1201,13 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>46461</v>
       </c>
@@ -1225,7 +1218,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46254</v>
       </c>
@@ -1239,7 +1232,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>46371</v>
       </c>
@@ -1247,13 +1240,13 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>46336</v>
       </c>
@@ -1261,13 +1254,13 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>46302</v>
       </c>
@@ -1281,7 +1274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>46402</v>
       </c>
@@ -1292,7 +1285,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>46305</v>
       </c>
@@ -1300,13 +1293,13 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <v>46320</v>
       </c>
@@ -1314,13 +1307,13 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>46270</v>
       </c>
@@ -1334,7 +1327,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>46310</v>
       </c>
@@ -1342,13 +1335,13 @@
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A31" s="2">
         <v>46275</v>
       </c>
@@ -1362,7 +1355,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>46310</v>
       </c>
@@ -1376,7 +1369,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>46301</v>
       </c>
@@ -1390,7 +1383,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A34" s="2">
         <v>46295</v>
       </c>
@@ -1404,7 +1397,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>46290</v>
       </c>
@@ -1418,7 +1411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>46254</v>
       </c>
@@ -1432,7 +1425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>46272</v>
       </c>
@@ -1446,7 +1439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A38" s="2">
         <v>46285</v>
       </c>
@@ -1460,7 +1453,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>46300</v>
       </c>
@@ -1474,7 +1467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>46310</v>
       </c>
@@ -1488,7 +1481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
         <v>46320</v>
       </c>
@@ -1502,7 +1495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>46331</v>
       </c>
@@ -1510,13 +1503,13 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D42" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>46341</v>
       </c>
@@ -1524,13 +1517,13 @@
         <v>49</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D43" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <v>46361</v>
       </c>
@@ -1541,7 +1534,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
         <v>46385</v>
       </c>
@@ -1552,7 +1545,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>46401</v>
       </c>
@@ -1563,7 +1556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
         <v>46382</v>
       </c>
@@ -1574,7 +1567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>46371</v>
       </c>
@@ -1585,7 +1578,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
         <v>46320</v>
       </c>
@@ -1593,13 +1586,13 @@
         <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D49" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>46265</v>
       </c>
@@ -1613,7 +1606,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>46290</v>
       </c>
@@ -1627,7 +1620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>46295</v>
       </c>
@@ -1641,7 +1634,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>46326</v>
       </c>
@@ -1652,7 +1645,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>46326</v>
       </c>
@@ -1663,7 +1656,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
         <v>46346</v>
       </c>
@@ -1674,7 +1667,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
         <v>46366</v>
       </c>
@@ -1685,7 +1678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>46385</v>
       </c>
@@ -1696,7 +1689,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>46285</v>
       </c>
@@ -1710,7 +1703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
         <v>46305</v>
       </c>
@@ -1724,7 +1717,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>46305</v>
       </c>
@@ -1732,13 +1725,13 @@
         <v>67</v>
       </c>
       <c r="C60" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>46315</v>
       </c>
@@ -1749,7 +1742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
         <v>46326</v>
       </c>
@@ -1760,7 +1753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
         <v>46277</v>
       </c>
@@ -1774,7 +1767,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
         <v>46295</v>
       </c>
@@ -1788,7 +1781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>46275</v>
       </c>
@@ -1802,7 +1795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>46265</v>
       </c>
@@ -1816,7 +1809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>46320</v>
       </c>
@@ -1824,27 +1817,27 @@
         <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D67" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>46315</v>
       </c>
       <c r="B68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C68" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D68" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>46300</v>
       </c>
@@ -1858,7 +1851,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
         <v>46295</v>
       </c>
@@ -1872,7 +1865,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
         <v>46303</v>
       </c>
@@ -1886,7 +1879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
         <v>46310</v>
       </c>
@@ -1894,13 +1887,13 @@
         <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D72" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
         <v>46310</v>
       </c>
@@ -1908,13 +1901,13 @@
         <v>81</v>
       </c>
       <c r="C73" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D73" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>46371</v>
       </c>
@@ -1922,13 +1915,13 @@
         <v>89</v>
       </c>
       <c r="C74" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D74" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
         <v>46376</v>
       </c>
@@ -1936,13 +1929,13 @@
         <v>90</v>
       </c>
       <c r="C75" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D75" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
         <v>46376</v>
       </c>
@@ -1950,13 +1943,13 @@
         <v>91</v>
       </c>
       <c r="C76" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D76" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
         <v>46341</v>
       </c>
@@ -1964,13 +1957,13 @@
         <v>92</v>
       </c>
       <c r="C77" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>46305</v>
       </c>
@@ -1984,7 +1977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
         <v>46317</v>
       </c>
@@ -1995,7 +1988,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>46302</v>
       </c>
@@ -2006,7 +1999,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>46295</v>
       </c>
@@ -2020,7 +2013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>46315</v>
       </c>
@@ -2031,7 +2024,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
         <v>46302</v>
       </c>
@@ -2042,7 +2035,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>46310</v>
       </c>
@@ -2053,7 +2046,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>46320</v>
       </c>
@@ -2064,12 +2057,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>46323</v>
       </c>
       <c r="B86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C86" t="s">
         <v>4</v>
@@ -2078,18 +2071,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>46300</v>
       </c>
       <c r="B87" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D87" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>46305</v>
       </c>
@@ -2100,7 +2093,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
         <v>46295</v>
       </c>
@@ -2111,7 +2104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>46305</v>
       </c>
@@ -2122,7 +2115,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>46320</v>
       </c>
@@ -2133,7 +2126,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>46301</v>
       </c>
@@ -2147,7 +2140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>46310</v>
       </c>
@@ -2158,7 +2151,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>46320</v>
       </c>
@@ -2169,7 +2162,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>46331</v>
       </c>
@@ -2177,13 +2170,13 @@
         <v>114</v>
       </c>
       <c r="C95" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D95" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>46300</v>
       </c>
@@ -2194,7 +2187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>46305</v>
       </c>
@@ -2205,7 +2198,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>46305</v>
       </c>
@@ -2216,7 +2209,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>46315</v>
       </c>
@@ -2227,7 +2220,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
         <v>46290</v>
       </c>
@@ -2238,7 +2231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>46305</v>
       </c>
@@ -2249,7 +2242,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>46295</v>
       </c>
@@ -2260,7 +2253,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
         <v>46326</v>
       </c>
@@ -2271,59 +2264,62 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B104" t="s">
         <v>123</v>
       </c>
+      <c r="C104" t="s">
+        <v>4</v>
+      </c>
       <c r="D104" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
-        <v>47390</v>
+        <v>46300</v>
       </c>
       <c r="B105" t="s">
         <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>125</v>
+        <v>4</v>
       </c>
       <c r="D105" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>46356</v>
       </c>
       <c r="B106" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D106" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>46370</v>
       </c>
       <c r="B107" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D107" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>46315</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" t="s">
@@ -2332,12 +2328,12 @@
       <c r="E108" s="5"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
         <v>46310</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
@@ -2346,12 +2342,12 @@
       <c r="F109" s="5"/>
       <c r="G109" s="6"/>
     </row>
-    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>46320</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D110" t="s">
         <v>15</v>

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="689" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78DABA6C-131C-40EB-830F-A82F9A3BCF73}"/>
+  <xr:revisionPtr revIDLastSave="767" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01A15F89-2D61-49C7-A4B4-4609428DA755}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="168">
   <si>
     <t>Date</t>
   </si>
@@ -41,90 +44,123 @@
     <t>Activity</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Responsibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotbox - all 4 walls erection completion </t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>ME</t>
+  </si>
+  <si>
+    <t>UNIT#3 hot box Side plate erection by 03.08.26</t>
+  </si>
+  <si>
+    <t>ISH Foundation handover</t>
+  </si>
+  <si>
+    <t>CCD</t>
+  </si>
+  <si>
+    <t>Boiler DHT - Target completion</t>
+  </si>
+  <si>
+    <t>1st HT Switchgear charging</t>
+  </si>
+  <si>
+    <t>EED</t>
+  </si>
+  <si>
+    <t>2nd TDBP Deck Casting</t>
+  </si>
+  <si>
+    <t>MPH Columns casting completion and scaffolding removal</t>
+  </si>
+  <si>
+    <t>Transfer Tower Foundation handover</t>
+  </si>
+  <si>
+    <t>Delayed R0 - 15-09-26/15-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tripper floor - 50% structure works completion </t>
+  </si>
+  <si>
+    <t>Delayed R0 - 25.08.26/15.09.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESP-CR 8.5m structure works completion </t>
+  </si>
+  <si>
+    <t>AHP Stg-2 Foundation handover</t>
+  </si>
+  <si>
     <t>TG Box up - Target completion</t>
   </si>
   <si>
-    <t>UNIT#3 hot box Side plate erection by 03.08.26</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Status</t>
+    <t>Delayed R0 - 31-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESP-CR 8.5Mm slab casting </t>
   </si>
   <si>
     <t>TG Oil Flushing completion</t>
   </si>
   <si>
+    <t>Delayed R0 - 31.10.26,18.11.26</t>
+  </si>
+  <si>
+    <t>C&amp;T</t>
+  </si>
+  <si>
     <t>Boiler Light up</t>
   </si>
   <si>
+    <t>Delayed - 15.11.26</t>
+  </si>
+  <si>
     <t xml:space="preserve">Steam Blowing Completion </t>
   </si>
   <si>
+    <t>Delayed - 15.12.26</t>
+  </si>
+  <si>
     <t>Sync</t>
   </si>
   <si>
+    <t>Delayed - 07.02.27</t>
+  </si>
+  <si>
     <t>Full Load</t>
   </si>
   <si>
+    <t>Delayed - 25.02.27</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trial Operation </t>
   </si>
   <si>
-    <t>Responsibility</t>
-  </si>
-  <si>
-    <t>Boiler DHT - Target completion</t>
-  </si>
-  <si>
-    <t>1st HT Switchgear charging</t>
-  </si>
-  <si>
-    <t>ME</t>
-  </si>
-  <si>
-    <t>EED</t>
-  </si>
-  <si>
-    <t>CCD</t>
-  </si>
-  <si>
-    <t>C&amp;T</t>
-  </si>
-  <si>
-    <t>2nd TDBP Deck Casting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotbox - all 4 walls erection completion </t>
-  </si>
-  <si>
-    <t>MPH Columns casting completion and scaffolding removal</t>
-  </si>
-  <si>
-    <t>ISH Foundation handover</t>
-  </si>
-  <si>
-    <t>Transfer Tower Foundation handover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESP-CR 8.5m structure works completion </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESP-CR 8.5Mm slab casting </t>
-  </si>
-  <si>
-    <t>Start of LP Turbine erection after hotbox completion</t>
-  </si>
-  <si>
     <t>Hotbox bottom plate erection</t>
   </si>
   <si>
     <t>Chimney 5th segment erection</t>
   </si>
   <si>
+    <t>Delayed - 30.11.26</t>
+  </si>
+  <si>
     <t>Chimney 4th segment erection</t>
   </si>
   <si>
+    <t>Delayed - 26.10.26</t>
+  </si>
+  <si>
     <t>Chimney 3rd segment erection</t>
   </si>
   <si>
@@ -134,21 +170,33 @@
     <t xml:space="preserve">CER to ESP RHS Foundation completion </t>
   </si>
   <si>
+    <t>Delayed -30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.10.26</t>
+  </si>
+  <si>
     <t xml:space="preserve">CER to ESP LHS Foundation completion </t>
   </si>
   <si>
+    <t>Delayed -30.06.26/15.07.26/30.07.26/14.08.26/05.09.26</t>
+  </si>
+  <si>
     <t xml:space="preserve">CER to Boiler Foundation completion </t>
   </si>
   <si>
     <t>ESP to ESP Control Room (LHS) – Electromech/RVPR</t>
   </si>
   <si>
+    <t>Delayed -30.07.26/20.08.26/10.09.26</t>
+  </si>
+  <si>
     <t>ESP to ESP Control Room (RHS)</t>
   </si>
   <si>
     <t>FD 3A foundation completion</t>
   </si>
   <si>
+    <t>Delayed - 30.08.26/30.09.26</t>
+  </si>
+  <si>
     <t xml:space="preserve">PA 3A foundation completion </t>
   </si>
   <si>
@@ -158,6 +206,9 @@
     <t>AHP MCC3 panel erection front</t>
   </si>
   <si>
+    <t>Delayed - R0 - 15.09.26</t>
+  </si>
+  <si>
     <t xml:space="preserve">Surge hopper foundation completion </t>
   </si>
   <si>
@@ -173,18 +224,27 @@
     <t>ACC - Street 1 ATT</t>
   </si>
   <si>
+    <t>Delayed - 20.09.26</t>
+  </si>
+  <si>
     <t>ACC - Street 3 ATT</t>
   </si>
   <si>
-    <t>Delayed - R0 - 25.08.26</t>
+    <t>Delayed - 30.09.26</t>
   </si>
   <si>
     <t>ACC - Street 4 ATT</t>
   </si>
   <si>
+    <t>Delayed - 25.10.26</t>
+  </si>
+  <si>
     <t>ACC - Street 5 ATT</t>
   </si>
   <si>
+    <t>Delayed - 05.11.26</t>
+  </si>
+  <si>
     <t>ACC - Street 6 ATT</t>
   </si>
   <si>
@@ -197,15 +257,15 @@
     <t>ACC - Common Duct ATT</t>
   </si>
   <si>
-    <t>Delayed R0 - 31-08-26</t>
-  </si>
-  <si>
     <t>MDBP Trial in RC</t>
   </si>
   <si>
     <t>MDBP motor trial</t>
   </si>
   <si>
+    <t>Delayed -17.10.26</t>
+  </si>
+  <si>
     <t xml:space="preserve">Street 1 ACC erection completion </t>
   </si>
   <si>
@@ -236,18 +296,21 @@
     <t>Street 4 Riser erection</t>
   </si>
   <si>
+    <t>Delayed - 14-09-26</t>
+  </si>
+  <si>
     <t>Street 5 Riser erection</t>
   </si>
   <si>
+    <t>Delayed - 30-09-26</t>
+  </si>
+  <si>
     <t>Street 6 Riser erection</t>
   </si>
   <si>
     <t>Street 7 Riser erection</t>
   </si>
   <si>
-    <t xml:space="preserve">Tripper floor - 50% structure works completion </t>
-  </si>
-  <si>
     <t>7AB gallery erection</t>
   </si>
   <si>
@@ -263,75 +326,69 @@
     <t>0BE Board charging</t>
   </si>
   <si>
+    <t>Delayed - 23.09.26/30.09.26</t>
+  </si>
+  <si>
+    <t>3.3KV - 3CA Board charging</t>
+  </si>
+  <si>
+    <t>Delayed - 26.09.26/10.10.26/20.10.26</t>
+  </si>
+  <si>
     <t>3BA Board charging</t>
   </si>
   <si>
+    <t>Delayed - 29.09.26/05.10.26</t>
+  </si>
+  <si>
     <t>3BB Board charging</t>
   </si>
   <si>
+    <t>Delayed - 16.09.26/30.09.26</t>
+  </si>
+  <si>
     <t>ST-2 charging</t>
   </si>
   <si>
     <t>UAT-3A charging</t>
   </si>
   <si>
-    <t>Delayed R0 - 05-09-26</t>
+    <t>Delayed - 15.09.26/30.09.26/15.10.26</t>
   </si>
   <si>
     <t>Start of TG Lube oil flushing</t>
   </si>
   <si>
-    <t>Delayed - 30.08.26/30.09.26</t>
-  </si>
-  <si>
-    <t>Delayed R0 - 25.08.26/15.09.26</t>
-  </si>
-  <si>
-    <t>Delayed - R0 - 15.09.26</t>
-  </si>
-  <si>
-    <t>Delayed - 20.09.26</t>
-  </si>
-  <si>
-    <t>Delayed - 30.09.26</t>
-  </si>
-  <si>
-    <t>Delayed - 14-09-26</t>
-  </si>
-  <si>
-    <t>Delayed - 29.09.26</t>
+    <t>Delayed - 05.10.26</t>
   </si>
   <si>
     <t>MS Line Hydro Test</t>
   </si>
   <si>
+    <t>Delayed -15.11.26</t>
+  </si>
+  <si>
     <t>HRH Line Hydro Test</t>
   </si>
   <si>
+    <t>Delayed -30.11.26</t>
+  </si>
+  <si>
     <t>CRH Line Hydro Test</t>
   </si>
   <si>
+    <t>Delayed -25.11.26</t>
+  </si>
+  <si>
     <t>BFD/BFR/BFS Hydro Test</t>
   </si>
   <si>
-    <t>Delayed - 10.09.26/20.09.26</t>
-  </si>
-  <si>
-    <t>Delayed - 16.09.26</t>
-  </si>
-  <si>
-    <t>Delayed -01.09.26/10.09.26/25.09.26</t>
+    <t>Delayed -31.10.26</t>
   </si>
   <si>
     <t xml:space="preserve">Eco Hopper erection </t>
   </si>
   <si>
-    <t>Delayed - 30.08.26/15.09.26/25.09.26/28.09.26</t>
-  </si>
-  <si>
-    <t>AHP Stg-2 Foundation handover</t>
-  </si>
-  <si>
     <t>Condenser pit staircase completion</t>
   </si>
   <si>
@@ -353,6 +410,12 @@
     <t xml:space="preserve">MPH C row sheeting works completion </t>
   </si>
   <si>
+    <t>Boiler TG Interconnection beam works from civil side</t>
+  </si>
+  <si>
+    <t>Electrical - 250 manpower by Shriram</t>
+  </si>
+  <si>
     <t xml:space="preserve">MOT, TG ECW- Cable tray completion </t>
   </si>
   <si>
@@ -368,12 +431,12 @@
     <t>Mot AOP, Centrifuge and MDBP LOP trial</t>
   </si>
   <si>
-    <t>Delayed - 20.09.26/27.09.26</t>
-  </si>
-  <si>
     <t xml:space="preserve">0DC Board charging </t>
   </si>
   <si>
+    <t>Delayed - 15.10.26</t>
+  </si>
+  <si>
     <t>3DB-TMCC Charging</t>
   </si>
   <si>
@@ -410,100 +473,73 @@
     <t>PA Fan 3A casting completion</t>
   </si>
   <si>
-    <t>Delayed -30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.10.26</t>
-  </si>
-  <si>
-    <t>Delayed -30.06.26/15.07.26/30.07.26/14.08.26/05.09.26</t>
-  </si>
-  <si>
-    <t>Delayed -30.07.26/20.08.26/10.09.26</t>
-  </si>
-  <si>
-    <t>Delayed - 30-09-26</t>
-  </si>
-  <si>
-    <t>Delayed - 15.09.26/30.09.26</t>
-  </si>
-  <si>
-    <t>Delayed - 25.10.26</t>
-  </si>
-  <si>
-    <t>Delayed - 05.11.26</t>
-  </si>
-  <si>
-    <t>Delayed -17.10.26</t>
-  </si>
-  <si>
-    <t>Delayed -31.10.26</t>
-  </si>
-  <si>
     <t>ID Fan motor trial</t>
   </si>
   <si>
-    <t>Delayed -15.11.26</t>
-  </si>
-  <si>
-    <t>Delayed -30.11.26</t>
-  </si>
-  <si>
-    <t>Delayed -25.11.26</t>
-  </si>
-  <si>
     <t>TG Barring</t>
   </si>
   <si>
-    <t>Delayed - 15.11.26</t>
-  </si>
-  <si>
-    <t>Delayed R0 - 31.10.26,18.11.26</t>
-  </si>
-  <si>
-    <t>Delayed - 15.12.26</t>
-  </si>
-  <si>
-    <t>Delayed - 07.02.27</t>
-  </si>
-  <si>
-    <t>Delayed - 25.02.27</t>
-  </si>
-  <si>
-    <t>Delayed - 26.09.26/10.10.26</t>
-  </si>
-  <si>
-    <t>3.3KV - 3CA Board charging</t>
+    <t>Deaerator - HT</t>
+  </si>
+  <si>
+    <t>SG ECW lines readiness for HT</t>
   </si>
   <si>
     <t>TG ECW Lines readiness for HT</t>
   </si>
   <si>
-    <t>Deaerator - HT</t>
-  </si>
-  <si>
-    <t>SG ECW lines readiness for HT</t>
-  </si>
-  <si>
-    <t>Delayed - 05.10.26</t>
-  </si>
-  <si>
-    <t>Electrical - 250 manpower by Shriram</t>
-  </si>
-  <si>
-    <t>Delayed - 23.09.26/30.09.26</t>
-  </si>
-  <si>
-    <t>Boiler TG Interconnection beam works from civil side</t>
-  </si>
-  <si>
-    <t>Delayed R0 - 15-09-26/15-10-26</t>
-  </si>
-  <si>
-    <t>Delayed - 30.11.26</t>
-  </si>
-  <si>
-    <t>Delayed - 26.10.26</t>
-  </si>
-  <si>
-    <t>Delayed R0 - 30.08.26/30.09.26</t>
+    <t>MOT VEF - A  load trial</t>
+  </si>
+  <si>
+    <t>MOT Room &amp; Oil Canal mulsifier system readiness (Sprinkler flushing)</t>
+  </si>
+  <si>
+    <t>Seal Oil Skid mulsifier system readiness</t>
+  </si>
+  <si>
+    <t>DCS Readiness from Siemens for Lube oil flushing</t>
+  </si>
+  <si>
+    <t>MOT &amp; SOST Internal cleaning &amp; inspection</t>
+  </si>
+  <si>
+    <t>Permanent lighting in Oil canal</t>
+  </si>
+  <si>
+    <t>MOT Cleaning and Oil Filling</t>
+  </si>
+  <si>
+    <t>Starting Oil flushing (Supply &amp; Return oil lines flushing)</t>
+  </si>
+  <si>
+    <t>Seal oil System Piping readiness for cardboard bursting</t>
+  </si>
+  <si>
+    <t>Seal oil System Piping complete readiness (for flushing)</t>
+  </si>
+  <si>
+    <t>MDBFP Lube oil flushing</t>
+  </si>
+  <si>
+    <t>ECW Overhead Tank &amp; Piping readiness</t>
+  </si>
+  <si>
+    <t>ECW Overhead Tank Normal Makeup and Emergency Makeup Readiness</t>
+  </si>
+  <si>
+    <t>TG and SG ECW Pumps Motor no load Trial</t>
+  </si>
+  <si>
+    <t>TG ECW Pump-A/B/C load Trial</t>
+  </si>
+  <si>
+    <t>ACW Piping completion and load trial</t>
+  </si>
+  <si>
+    <t>Delayed - 10.09.26/20.09.26/30.09.26</t>
+  </si>
+  <si>
+    <t>Delayed - 30.09.26/10.10.26</t>
   </si>
 </sst>
 </file>
@@ -599,7 +635,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -615,6 +651,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -918,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -935,10 +974,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
@@ -946,13 +985,13 @@
         <v>46259</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -960,13 +999,13 @@
         <v>46237</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
@@ -974,13 +1013,13 @@
         <v>46244</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
@@ -988,13 +1027,13 @@
         <v>46251</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
@@ -1002,13 +1041,13 @@
         <v>46280</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
@@ -1016,13 +1055,13 @@
         <v>46269</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
@@ -1030,13 +1069,13 @@
         <v>46251</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
@@ -1044,13 +1083,13 @@
         <v>46341</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
@@ -1058,13 +1097,13 @@
         <v>46295</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
@@ -1072,13 +1111,13 @@
         <v>46290</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
@@ -1086,13 +1125,13 @@
         <v>46305</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>156</v>
+        <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
@@ -1100,13 +1139,13 @@
         <v>46356</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
@@ -1114,13 +1153,13 @@
         <v>46295</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
@@ -1128,13 +1167,13 @@
         <v>46280</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
@@ -1142,13 +1181,13 @@
         <v>46366</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
@@ -1156,13 +1195,13 @@
         <v>46381</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
@@ -1170,13 +1209,13 @@
         <v>46402</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
@@ -1184,13 +1223,13 @@
         <v>46444</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
@@ -1198,13 +1237,13 @@
         <v>46456</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
@@ -1212,10 +1251,10 @@
         <v>46461</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
@@ -1223,13 +1262,13 @@
         <v>46254</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
@@ -1237,13 +1276,13 @@
         <v>46371</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
@@ -1251,13 +1290,13 @@
         <v>46336</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
@@ -1265,13 +1304,13 @@
         <v>46302</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
@@ -1279,10 +1318,10 @@
         <v>46402</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
@@ -1290,13 +1329,13 @@
         <v>46305</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
@@ -1304,13 +1343,13 @@
         <v>46320</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
@@ -1318,13 +1357,13 @@
         <v>46270</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
@@ -1332,13 +1371,13 @@
         <v>46310</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
@@ -1346,13 +1385,13 @@
         <v>46275</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
@@ -1360,13 +1399,13 @@
         <v>46310</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
@@ -1374,13 +1413,13 @@
         <v>46301</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
@@ -1388,13 +1427,13 @@
         <v>46295</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
@@ -1402,13 +1441,13 @@
         <v>46290</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
@@ -1416,13 +1455,13 @@
         <v>46254</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C36" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
@@ -1430,13 +1469,13 @@
         <v>46272</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C37" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
@@ -1444,13 +1483,13 @@
         <v>46285</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
@@ -1458,13 +1497,13 @@
         <v>46300</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
@@ -1472,13 +1511,13 @@
         <v>46310</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
@@ -1486,13 +1525,13 @@
         <v>46320</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
@@ -1500,13 +1539,13 @@
         <v>46331</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="D42" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
@@ -1514,13 +1553,13 @@
         <v>46341</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C43" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
@@ -1528,10 +1567,10 @@
         <v>46361</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
@@ -1539,10 +1578,10 @@
         <v>46385</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
@@ -1550,10 +1589,10 @@
         <v>46401</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
@@ -1561,10 +1600,10 @@
         <v>46382</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
@@ -1572,10 +1611,10 @@
         <v>46371</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
@@ -1583,13 +1622,13 @@
         <v>46320</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
@@ -1597,13 +1636,13 @@
         <v>46265</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
@@ -1611,27 +1650,27 @@
         <v>46290</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
-        <v>46295</v>
+        <v>46310</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C52" t="s">
-        <v>93</v>
+        <v>166</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
@@ -1639,10 +1678,10 @@
         <v>46326</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D53" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
@@ -1650,10 +1689,10 @@
         <v>46326</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
@@ -1661,10 +1700,10 @@
         <v>46346</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D55" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
@@ -1672,10 +1711,10 @@
         <v>46366</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
@@ -1683,10 +1722,10 @@
         <v>46385</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D57" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.45">
@@ -1694,13 +1733,13 @@
         <v>46285</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C58" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D58" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.45">
@@ -1708,13 +1747,13 @@
         <v>46305</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D59" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
@@ -1722,13 +1761,13 @@
         <v>46305</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C60" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="D60" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
@@ -1736,10 +1775,10 @@
         <v>46315</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
@@ -1747,10 +1786,10 @@
         <v>46326</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.45">
@@ -1758,27 +1797,27 @@
         <v>46277</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C63" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
-        <v>46295</v>
+        <v>46308</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="D64" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
@@ -1786,13 +1825,13 @@
         <v>46275</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C65" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D65" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
@@ -1800,13 +1839,13 @@
         <v>46265</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C66" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
@@ -1814,83 +1853,83 @@
         <v>46320</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C67" t="s">
-        <v>151</v>
+        <v>96</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
-        <v>46315</v>
+        <v>46331</v>
       </c>
       <c r="B68" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="C68" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
-        <v>46300</v>
+        <v>46325</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C69" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
-        <v>46295</v>
+        <v>46308</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C70" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D70" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="B71" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C71" t="s">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
-        <v>46310</v>
+        <v>46330</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C72" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
@@ -1898,13 +1937,13 @@
         <v>46310</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="D73" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
@@ -1912,13 +1951,13 @@
         <v>46371</v>
       </c>
       <c r="B74" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C74" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
@@ -1926,13 +1965,13 @@
         <v>46376</v>
       </c>
       <c r="B75" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C75" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="D75" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.45">
@@ -1940,13 +1979,13 @@
         <v>46376</v>
       </c>
       <c r="B76" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C76" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="D76" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.45">
@@ -1954,27 +1993,27 @@
         <v>46341</v>
       </c>
       <c r="B77" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C77" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D77" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="C78" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.45">
@@ -1982,10 +2021,10 @@
         <v>46317</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D79" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.45">
@@ -1993,10 +2032,10 @@
         <v>46302</v>
       </c>
       <c r="B80" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="D80" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
@@ -2004,13 +2043,13 @@
         <v>46295</v>
       </c>
       <c r="B81" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C81" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D81" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
@@ -2018,10 +2057,10 @@
         <v>46315</v>
       </c>
       <c r="B82" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="D82" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.45">
@@ -2029,10 +2068,10 @@
         <v>46302</v>
       </c>
       <c r="B83" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D83" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.45">
@@ -2040,10 +2079,10 @@
         <v>46310</v>
       </c>
       <c r="B84" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D84" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.45">
@@ -2051,10 +2090,10 @@
         <v>46320</v>
       </c>
       <c r="B85" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="D85" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.45">
@@ -2062,13 +2101,13 @@
         <v>46323</v>
       </c>
       <c r="B86" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="C86" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D86" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.45">
@@ -2076,10 +2115,10 @@
         <v>46300</v>
       </c>
       <c r="B87" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D87" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.45">
@@ -2087,10 +2126,10 @@
         <v>46305</v>
       </c>
       <c r="B88" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
@@ -2098,10 +2137,10 @@
         <v>46295</v>
       </c>
       <c r="B89" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="D89" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.45">
@@ -2109,10 +2148,10 @@
         <v>46305</v>
       </c>
       <c r="B90" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="D90" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
@@ -2120,10 +2159,10 @@
         <v>46320</v>
       </c>
       <c r="B91" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.45">
@@ -2131,35 +2170,41 @@
         <v>46301</v>
       </c>
       <c r="B92" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C92" t="s">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
-        <v>46310</v>
+        <v>46320</v>
       </c>
       <c r="B93" t="s">
-        <v>112</v>
+        <v>131</v>
+      </c>
+      <c r="C93" t="s">
+        <v>132</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
-        <v>46320</v>
+        <v>46325</v>
       </c>
       <c r="B94" t="s">
-        <v>113</v>
+        <v>133</v>
+      </c>
+      <c r="C94" t="s">
+        <v>66</v>
       </c>
       <c r="D94" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.45">
@@ -2167,13 +2212,13 @@
         <v>46331</v>
       </c>
       <c r="B95" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C95" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="D95" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.45">
@@ -2181,10 +2226,10 @@
         <v>46300</v>
       </c>
       <c r="B96" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="D96" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.45">
@@ -2192,10 +2237,10 @@
         <v>46305</v>
       </c>
       <c r="B97" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D97" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.45">
@@ -2203,10 +2248,10 @@
         <v>46305</v>
       </c>
       <c r="B98" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="D98" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.45">
@@ -2214,10 +2259,10 @@
         <v>46315</v>
       </c>
       <c r="B99" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D99" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
@@ -2225,10 +2270,10 @@
         <v>46290</v>
       </c>
       <c r="B100" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D100" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.45">
@@ -2236,10 +2281,10 @@
         <v>46305</v>
       </c>
       <c r="B101" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D101" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
@@ -2247,10 +2292,10 @@
         <v>46295</v>
       </c>
       <c r="B102" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="D102" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.45">
@@ -2258,10 +2303,10 @@
         <v>46326</v>
       </c>
       <c r="B103" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="D103" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
@@ -2269,13 +2314,13 @@
         <v>46300</v>
       </c>
       <c r="B104" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C104" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D104" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
@@ -2283,13 +2328,13 @@
         <v>46300</v>
       </c>
       <c r="B105" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="C105" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D105" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.45">
@@ -2297,10 +2342,10 @@
         <v>46356</v>
       </c>
       <c r="B106" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
@@ -2308,10 +2353,10 @@
         <v>46370</v>
       </c>
       <c r="B107" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
@@ -2323,7 +2368,7 @@
       </c>
       <c r="C108" s="4"/>
       <c r="D108" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E108" s="5"/>
       <c r="F108" s="6"/>
@@ -2336,7 +2381,7 @@
         <v>148</v>
       </c>
       <c r="D109" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E109" s="7"/>
       <c r="F109" s="5"/>
@@ -2344,17 +2389,154 @@
     </row>
     <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
-        <v>46320</v>
+        <v>46325</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
+      </c>
+      <c r="C110" t="s">
+        <v>66</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
       <c r="G110" s="6"/>
+    </row>
+    <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A111" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D111" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A112" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A113" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A114" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A115" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A116" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A117" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A118" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A119" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A120" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A121" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A122" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A123" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A124" s="2">
+        <v>46332</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A125" s="2">
+        <v>46337</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A126" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="B127" s="8"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D21">

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="767" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01A15F89-2D61-49C7-A4B4-4609428DA755}"/>
+  <xr:revisionPtr revIDLastSave="816" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42BF3360-300D-4707-BDF7-5715E51D6C82}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="180">
   <si>
     <t>Date</t>
   </si>
@@ -540,6 +540,42 @@
   </si>
   <si>
     <t>Delayed - 30.09.26/10.10.26</t>
+  </si>
+  <si>
+    <t>TDBP EOT Commissioning</t>
+  </si>
+  <si>
+    <t>TDBP 2B DRIVE Turbine placement</t>
+  </si>
+  <si>
+    <t>Commissioning</t>
+  </si>
+  <si>
+    <t>C&amp;I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPT boxup </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPT Rotor placement </t>
+  </si>
+  <si>
+    <t>LPT inner casing bottom half placement–Start from 23-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPT Outer casing top half placement, and checking </t>
+  </si>
+  <si>
+    <t>Delayed - 20.10.26</t>
+  </si>
+  <si>
+    <t>150 manpower by alternate agency M/s M&amp;S in Piping scope</t>
+  </si>
+  <si>
+    <t>Delayed -30.09.26</t>
+  </si>
+  <si>
+    <t>Delayed - 10.10.26</t>
   </si>
 </sst>
 </file>
@@ -635,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -654,6 +690,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -957,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1150,13 +1189,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
-        <v>46295</v>
+        <v>46312</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>5</v>
+        <v>178</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
@@ -2234,10 +2273,13 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
-        <v>46305</v>
+        <v>46315</v>
       </c>
       <c r="B97" t="s">
         <v>136</v>
+      </c>
+      <c r="C97" t="s">
+        <v>179</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
@@ -2361,12 +2403,14 @@
     </row>
     <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
-        <v>46315</v>
+        <v>46323</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C108" s="4"/>
+      <c r="C108" s="4" t="s">
+        <v>176</v>
+      </c>
       <c r="D108" t="s">
         <v>6</v>
       </c>
@@ -2422,121 +2466,240 @@
       <c r="B112" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D112" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>46321</v>
       </c>
       <c r="B113" s="8" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D113" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>46313</v>
       </c>
       <c r="B114" s="8" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D114" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>46311</v>
       </c>
       <c r="B115" s="8" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D115" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>46312</v>
       </c>
       <c r="B116" s="8" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D116" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>46312</v>
       </c>
       <c r="B117" s="8" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D117" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>46312</v>
       </c>
       <c r="B118" s="8" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D118" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A119" s="2">
         <v>46310</v>
       </c>
       <c r="B119" s="8" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D119" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
         <v>46314</v>
       </c>
       <c r="B120" s="8" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D120" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
         <v>46310</v>
       </c>
       <c r="B121" s="8" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D121" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>46320</v>
       </c>
       <c r="B122" s="8" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D122" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
         <v>46323</v>
       </c>
       <c r="B123" s="8" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D123" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>46332</v>
       </c>
       <c r="B124" s="8" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D124" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
         <v>46337</v>
       </c>
       <c r="B125" s="8" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D125" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>46325</v>
       </c>
       <c r="B126" s="8" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="B127" s="8"/>
+      <c r="D126" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A127" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D127" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A128" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D128" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A129" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D129" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A130" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D130" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A131" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D131" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A132" s="2">
+        <v>46336</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D132" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A133" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D133" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D21">

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="816" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42BF3360-300D-4707-BDF7-5715E51D6C82}"/>
+  <xr:revisionPtr revIDLastSave="861" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97A8FD92-7F0A-4F40-B039-A9C10371A767}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="192">
   <si>
     <t>Date</t>
   </si>
@@ -92,9 +92,6 @@
     <t xml:space="preserve">Tripper floor - 50% structure works completion </t>
   </si>
   <si>
-    <t>Delayed R0 - 25.08.26/15.09.26</t>
-  </si>
-  <si>
     <t xml:space="preserve">ESP-CR 8.5m structure works completion </t>
   </si>
   <si>
@@ -539,9 +536,6 @@
     <t>Delayed - 10.09.26/20.09.26/30.09.26</t>
   </si>
   <si>
-    <t>Delayed - 30.09.26/10.10.26</t>
-  </si>
-  <si>
     <t>TDBP EOT Commissioning</t>
   </si>
   <si>
@@ -576,13 +570,55 @@
   </si>
   <si>
     <t>Delayed - 10.10.26</t>
+  </si>
+  <si>
+    <t>Delayed - 30.09.26/10.10.26/15.10.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toggle duct erection </t>
+  </si>
+  <si>
+    <t>APH 3A erection start</t>
+  </si>
+  <si>
+    <t>APH 3B Lube oil flushing start</t>
+  </si>
+  <si>
+    <t>Delayed R0 - 25.08.26/15.09.26/30.09.26</t>
+  </si>
+  <si>
+    <t>FD 3B motor trial</t>
+  </si>
+  <si>
+    <t>Cable rack gallery erection completion upto FD 3A by </t>
+  </si>
+  <si>
+    <t>CR-11,12 cable rack foundation completion by (only bolt lift pending)</t>
+  </si>
+  <si>
+    <t>Approach to Boiler RHS from CR-11, 12 by </t>
+  </si>
+  <si>
+    <t>K row drain completion by </t>
+  </si>
+  <si>
+    <t>ESP 3 F pass inlet area paving completion by (Last commitment - 19-09-26)</t>
+  </si>
+  <si>
+    <t>Material removal near ESP-CR/ Chimney area for approach to ESP CR LHS transformer civil works by </t>
+  </si>
+  <si>
+    <t>ESP-CR LHS 4 nos transformer foundation civil works completion by </t>
+  </si>
+  <si>
+    <t>11m ESP-CR structure and deck sheeting completion by </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,6 +647,12 @@
     </font>
     <font>
       <sz val="6"/>
+      <color rgb="FF242424"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -671,7 +713,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -693,6 +735,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -996,16 +1050,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G133"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:G146"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1019,7 +1073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46259</v>
       </c>
@@ -1033,7 +1087,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46237</v>
       </c>
@@ -1047,7 +1101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46244</v>
       </c>
@@ -1061,7 +1115,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46251</v>
       </c>
@@ -1075,7 +1129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46280</v>
       </c>
@@ -1089,7 +1143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46269</v>
       </c>
@@ -1103,7 +1157,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46251</v>
       </c>
@@ -1117,7 +1171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46341</v>
       </c>
@@ -1131,26 +1185,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46295</v>
+        <v>46325</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46290</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -1159,12 +1213,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46305</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -1173,40 +1227,40 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46356</v>
       </c>
       <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
         <v>21</v>
       </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
       <c r="D13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>46312</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>46280</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -1215,93 +1269,93 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>46366</v>
       </c>
       <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
         <v>24</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>25</v>
       </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>46381</v>
       </c>
       <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
         <v>27</v>
       </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
       <c r="D17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>46402</v>
       </c>
       <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
         <v>29</v>
       </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
       <c r="D18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>46444</v>
       </c>
       <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
         <v>31</v>
       </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
       <c r="D19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>46456</v>
       </c>
       <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
       <c r="D20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46461</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46254</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -1310,40 +1364,40 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>46371</v>
       </c>
       <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
         <v>37</v>
       </c>
-      <c r="C23" t="s">
-        <v>38</v>
-      </c>
       <c r="D23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>46336</v>
       </c>
       <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
         <v>39</v>
       </c>
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
       <c r="D24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>46302</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>5</v>
@@ -1352,51 +1406,51 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>46402</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>46305</v>
       </c>
       <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
         <v>43</v>
       </c>
-      <c r="C27" t="s">
-        <v>44</v>
-      </c>
       <c r="D27" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>46320</v>
       </c>
       <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
         <v>45</v>
       </c>
-      <c r="C28" t="s">
-        <v>46</v>
-      </c>
       <c r="D28" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>46270</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -1405,26 +1459,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>46310</v>
       </c>
       <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
         <v>48</v>
       </c>
-      <c r="C30" t="s">
-        <v>49</v>
-      </c>
       <c r="D30" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>46275</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -1433,26 +1487,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>46310</v>
       </c>
       <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
         <v>51</v>
       </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
       <c r="D32" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>46301</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -1461,12 +1515,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>46295</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1475,26 +1529,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>46290</v>
       </c>
       <c r="B35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" t="s">
         <v>55</v>
       </c>
-      <c r="C35" t="s">
-        <v>56</v>
-      </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>46254</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1503,12 +1557,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>46272</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1517,12 +1571,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>46285</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -1531,12 +1585,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>46300</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -1545,137 +1599,137 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>46310</v>
       </c>
       <c r="B40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" t="s">
         <v>61</v>
       </c>
-      <c r="C40" t="s">
-        <v>62</v>
-      </c>
       <c r="D40" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>46320</v>
       </c>
       <c r="B41" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" t="s">
         <v>63</v>
       </c>
-      <c r="C41" t="s">
-        <v>64</v>
-      </c>
       <c r="D41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>46331</v>
       </c>
       <c r="B42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" t="s">
         <v>65</v>
       </c>
-      <c r="C42" t="s">
-        <v>66</v>
-      </c>
       <c r="D42" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>46341</v>
       </c>
       <c r="B43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" t="s">
         <v>67</v>
       </c>
-      <c r="C43" t="s">
-        <v>68</v>
-      </c>
       <c r="D43" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>46361</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D44" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>46385</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D45" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46401</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D46" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46382</v>
       </c>
       <c r="B47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D47" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>46371</v>
       </c>
       <c r="B48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D48" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>46320</v>
       </c>
       <c r="B49" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" t="s">
         <v>74</v>
-      </c>
-      <c r="C49" t="s">
-        <v>75</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>46265</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -1684,12 +1738,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>46290</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -1698,81 +1752,81 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>46310</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D52" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>46326</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D53" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>46326</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D54" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>46346</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D55" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>46366</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D56" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>46385</v>
       </c>
       <c r="B57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D57" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>46285</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -1781,62 +1835,62 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>46305</v>
       </c>
       <c r="B59" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" t="s">
         <v>85</v>
       </c>
-      <c r="C59" t="s">
-        <v>86</v>
-      </c>
       <c r="D59" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>46305</v>
       </c>
       <c r="B60" t="s">
+        <v>86</v>
+      </c>
+      <c r="C60" t="s">
         <v>87</v>
       </c>
-      <c r="C60" t="s">
-        <v>88</v>
-      </c>
       <c r="D60" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>46315</v>
       </c>
       <c r="B61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D61" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>46326</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D62" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>46277</v>
       </c>
       <c r="B63" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -1845,12 +1899,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>46308</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -1859,12 +1913,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>46275</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -1873,12 +1927,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>46265</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -1887,68 +1941,68 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>46320</v>
       </c>
       <c r="B67" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" t="s">
         <v>95</v>
-      </c>
-      <c r="C67" t="s">
-        <v>96</v>
       </c>
       <c r="D67" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>46331</v>
       </c>
       <c r="B68" t="s">
+        <v>96</v>
+      </c>
+      <c r="C68" t="s">
         <v>97</v>
-      </c>
-      <c r="C68" t="s">
-        <v>98</v>
       </c>
       <c r="D68" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>46325</v>
       </c>
       <c r="B69" t="s">
+        <v>98</v>
+      </c>
+      <c r="C69" t="s">
         <v>99</v>
-      </c>
-      <c r="C69" t="s">
-        <v>100</v>
       </c>
       <c r="D69" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>46308</v>
       </c>
       <c r="B70" t="s">
+        <v>100</v>
+      </c>
+      <c r="C70" t="s">
         <v>101</v>
-      </c>
-      <c r="C70" t="s">
-        <v>102</v>
       </c>
       <c r="D70" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>46305</v>
       </c>
       <c r="B71" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -1957,132 +2011,132 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>46330</v>
       </c>
       <c r="B72" t="s">
+        <v>103</v>
+      </c>
+      <c r="C72" t="s">
         <v>104</v>
-      </c>
-      <c r="C72" t="s">
-        <v>105</v>
       </c>
       <c r="D72" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>46310</v>
       </c>
       <c r="B73" t="s">
+        <v>105</v>
+      </c>
+      <c r="C73" t="s">
         <v>106</v>
       </c>
-      <c r="C73" t="s">
-        <v>107</v>
-      </c>
       <c r="D73" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>46371</v>
       </c>
       <c r="B74" t="s">
+        <v>107</v>
+      </c>
+      <c r="C74" t="s">
         <v>108</v>
       </c>
-      <c r="C74" t="s">
-        <v>109</v>
-      </c>
       <c r="D74" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>46376</v>
       </c>
       <c r="B75" t="s">
+        <v>109</v>
+      </c>
+      <c r="C75" t="s">
         <v>110</v>
       </c>
-      <c r="C75" t="s">
-        <v>111</v>
-      </c>
       <c r="D75" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>46376</v>
       </c>
       <c r="B76" t="s">
+        <v>111</v>
+      </c>
+      <c r="C76" t="s">
         <v>112</v>
       </c>
-      <c r="C76" t="s">
-        <v>113</v>
-      </c>
       <c r="D76" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>46341</v>
       </c>
       <c r="B77" t="s">
+        <v>113</v>
+      </c>
+      <c r="C77" t="s">
         <v>114</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B78" t="s">
         <v>115</v>
       </c>
-      <c r="D77" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A78" s="2">
-        <v>46310</v>
-      </c>
-      <c r="B78" t="s">
-        <v>116</v>
-      </c>
       <c r="C78" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D78" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>46317</v>
       </c>
       <c r="B79" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D79" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>46302</v>
       </c>
       <c r="B80" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>46295</v>
       </c>
       <c r="B81" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
@@ -2091,56 +2145,56 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>46315</v>
       </c>
       <c r="B82" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>46302</v>
       </c>
       <c r="B83" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D83" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>46310</v>
       </c>
       <c r="B84" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D84" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>46320</v>
       </c>
       <c r="B85" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D85" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>46323</v>
       </c>
       <c r="B86" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
@@ -2149,67 +2203,67 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>46300</v>
       </c>
       <c r="B87" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D87" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>46305</v>
       </c>
       <c r="B88" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D88" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>46295</v>
       </c>
       <c r="B89" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D89" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>46305</v>
       </c>
       <c r="B90" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D90" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>46320</v>
       </c>
       <c r="B91" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D91" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>46301</v>
       </c>
       <c r="B92" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
@@ -2218,145 +2272,148 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>46320</v>
       </c>
       <c r="B93" t="s">
+        <v>130</v>
+      </c>
+      <c r="C93" t="s">
         <v>131</v>
-      </c>
-      <c r="C93" t="s">
-        <v>132</v>
       </c>
       <c r="D93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>46325</v>
       </c>
       <c r="B94" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C94" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D94" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>46331</v>
       </c>
       <c r="B95" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C95" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D95" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>46300</v>
       </c>
       <c r="B96" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>46315</v>
       </c>
       <c r="B97" t="s">
+        <v>135</v>
+      </c>
+      <c r="C97" t="s">
+        <v>177</v>
+      </c>
+      <c r="D97" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B98" t="s">
         <v>136</v>
       </c>
-      <c r="C97" t="s">
-        <v>179</v>
-      </c>
-      <c r="D97" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A98" s="2">
-        <v>46305</v>
-      </c>
-      <c r="B98" t="s">
-        <v>137</v>
+      <c r="C98" t="s">
+        <v>177</v>
       </c>
       <c r="D98" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>46315</v>
       </c>
       <c r="B99" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>46290</v>
       </c>
       <c r="B100" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D100" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>46305</v>
       </c>
       <c r="B101" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D101" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>46295</v>
       </c>
       <c r="B102" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D102" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>46326</v>
       </c>
       <c r="B103" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D103" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>46300</v>
       </c>
       <c r="B104" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C104" t="s">
         <v>5</v>
@@ -2365,12 +2422,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>46300</v>
       </c>
       <c r="B105" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C105" t="s">
         <v>5</v>
@@ -2379,37 +2436,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>46356</v>
       </c>
       <c r="B106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D106" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>46370</v>
       </c>
       <c r="B107" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D107" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>46323</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D108" t="s">
         <v>6</v>
@@ -2417,12 +2474,12 @@
       <c r="E108" s="5"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>46310</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D109" t="s">
         <v>6</v>
@@ -2431,15 +2488,15 @@
       <c r="F109" s="5"/>
       <c r="G109" s="6"/>
     </row>
-    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>46325</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C110" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D110" t="s">
         <v>6</v>
@@ -2448,258 +2505,403 @@
       <c r="F110" s="5"/>
       <c r="G110" s="6"/>
     </row>
-    <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>46309</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D111" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>46311</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D112" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>46321</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D113" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>46313</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D114" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>46311</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D115" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>46312</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D116" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>46312</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D117" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>46312</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D118" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>46310</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D119" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>46314</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D120" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>46310</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D121" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>46320</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D122" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>46323</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D123" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>46332</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D124" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>46337</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D125" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>46325</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D126" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>46312</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D127" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>46313</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D128" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>46312</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D129" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>46318</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D130" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>46321</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D131" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>46336</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D132" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>46318</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D133" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>46333</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D134" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="2">
+        <v>46336</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D135" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B136" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D136" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D137" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C138" s="4"/>
+      <c r="D138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A139" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C139" s="4"/>
+      <c r="D139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C140" s="4"/>
+      <c r="D140" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A141" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C141" s="4"/>
+      <c r="D141" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C142" s="4"/>
+      <c r="D142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A143" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C143" s="4"/>
+      <c r="D143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <v>46336</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C144" s="10"/>
+      <c r="D144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C145" s="10"/>
+      <c r="D145" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A146" s="11"/>
+      <c r="B146" s="12"/>
+      <c r="C146" s="13"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D21">

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="861" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97A8FD92-7F0A-4F40-B039-A9C10371A767}"/>
+  <xr:revisionPtr revIDLastSave="886" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E14EB96-8EE4-46E5-8367-CDA1F68CD3F4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="194">
   <si>
     <t>Date</t>
   </si>
@@ -182,18 +182,12 @@
     <t>ESP to ESP Control Room (LHS) – Electromech/RVPR</t>
   </si>
   <si>
-    <t>Delayed -30.07.26/20.08.26/10.09.26</t>
-  </si>
-  <si>
     <t>ESP to ESP Control Room (RHS)</t>
   </si>
   <si>
     <t>FD 3A foundation completion</t>
   </si>
   <si>
-    <t>Delayed - 30.08.26/30.09.26</t>
-  </si>
-  <si>
     <t xml:space="preserve">PA 3A foundation completion </t>
   </si>
   <si>
@@ -293,15 +287,9 @@
     <t>Street 4 Riser erection</t>
   </si>
   <si>
-    <t>Delayed - 14-09-26</t>
-  </si>
-  <si>
     <t>Street 5 Riser erection</t>
   </si>
   <si>
-    <t>Delayed - 30-09-26</t>
-  </si>
-  <si>
     <t>Street 6 Riser erection</t>
   </si>
   <si>
@@ -612,6 +600,24 @@
   </si>
   <si>
     <t>11m ESP-CR structure and deck sheeting completion by </t>
+  </si>
+  <si>
+    <t>ACC - GT and IPBD foundation clearance</t>
+  </si>
+  <si>
+    <t>ACC - Clearance for cable rack structure</t>
+  </si>
+  <si>
+    <t>Delayed - 14-09-26/10-10-26</t>
+  </si>
+  <si>
+    <t>Delayed - 30-09-26/10-10-26</t>
+  </si>
+  <si>
+    <t>Delayed -30.07.26/20.08.26/10.09.26/15.10.26</t>
+  </si>
+  <si>
+    <t>Delayed - 30.08.26/30.09.26/15.10.26</t>
   </si>
 </sst>
 </file>
@@ -713,11 +719,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -730,9 +735,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -740,13 +742,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1050,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1193,7 +1195,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
@@ -1249,7 +1251,7 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
@@ -1260,7 +1262,7 @@
         <v>46280</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -1419,7 +1421,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>46305</v>
+        <v>46320</v>
       </c>
       <c r="B27" t="s">
         <v>42</v>
@@ -1461,24 +1463,24 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>46310</v>
+        <v>46326</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>192</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>46275</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>49</v>
+      <c r="B31" t="s">
+        <v>48</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -1489,13 +1491,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>46310</v>
+        <v>46326</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>193</v>
       </c>
       <c r="D32" t="s">
         <v>9</v>
@@ -1506,7 +1508,7 @@
         <v>46301</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -1515,12 +1517,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>46295</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>53</v>
+      <c r="B34" t="s">
+        <v>51</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1534,10 +1536,10 @@
         <v>46290</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
@@ -1548,7 +1550,7 @@
         <v>46254</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1562,7 +1564,7 @@
         <v>46272</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1571,12 +1573,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>46285</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>58</v>
+      <c r="B38" t="s">
+        <v>56</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -1590,7 +1592,7 @@
         <v>46300</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -1604,10 +1606,10 @@
         <v>46310</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D40" t="s">
         <v>6</v>
@@ -1618,10 +1620,10 @@
         <v>46320</v>
       </c>
       <c r="B41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D41" t="s">
         <v>6</v>
@@ -1632,10 +1634,10 @@
         <v>46331</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D42" t="s">
         <v>6</v>
@@ -1646,10 +1648,10 @@
         <v>46341</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D43" t="s">
         <v>6</v>
@@ -1660,7 +1662,7 @@
         <v>46361</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D44" t="s">
         <v>6</v>
@@ -1671,7 +1673,7 @@
         <v>46385</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
         <v>6</v>
@@ -1682,7 +1684,7 @@
         <v>46401</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D46" t="s">
         <v>6</v>
@@ -1693,7 +1695,7 @@
         <v>46382</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D47" t="s">
         <v>6</v>
@@ -1704,7 +1706,7 @@
         <v>46371</v>
       </c>
       <c r="B48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D48" t="s">
         <v>6</v>
@@ -1715,10 +1717,10 @@
         <v>46320</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C49" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
@@ -1729,7 +1731,7 @@
         <v>46265</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -1743,7 +1745,7 @@
         <v>46290</v>
       </c>
       <c r="B51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -1757,10 +1759,10 @@
         <v>46310</v>
       </c>
       <c r="B52" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D52" t="s">
         <v>6</v>
@@ -1771,7 +1773,7 @@
         <v>46326</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D53" t="s">
         <v>6</v>
@@ -1782,7 +1784,7 @@
         <v>46326</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D54" t="s">
         <v>6</v>
@@ -1793,7 +1795,7 @@
         <v>46346</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D55" t="s">
         <v>6</v>
@@ -1804,7 +1806,7 @@
         <v>46366</v>
       </c>
       <c r="B56" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D56" t="s">
         <v>6</v>
@@ -1815,7 +1817,7 @@
         <v>46385</v>
       </c>
       <c r="B57" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D57" t="s">
         <v>6</v>
@@ -1826,7 +1828,7 @@
         <v>46285</v>
       </c>
       <c r="B58" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -1837,13 +1839,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>46305</v>
+        <v>46320</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="D59" t="s">
         <v>6</v>
@@ -1851,13 +1853,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>46305</v>
+        <v>46326</v>
       </c>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C60" t="s">
-        <v>87</v>
+        <v>191</v>
       </c>
       <c r="D60" t="s">
         <v>6</v>
@@ -1868,7 +1870,7 @@
         <v>46315</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D61" t="s">
         <v>6</v>
@@ -1879,7 +1881,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D62" t="s">
         <v>6</v>
@@ -1890,7 +1892,7 @@
         <v>46277</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -1904,7 +1906,7 @@
         <v>46308</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -1918,7 +1920,7 @@
         <v>46275</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -1932,7 +1934,7 @@
         <v>46265</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -1946,10 +1948,10 @@
         <v>46320</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D67" t="s">
         <v>12</v>
@@ -1960,10 +1962,10 @@
         <v>46331</v>
       </c>
       <c r="B68" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C68" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D68" t="s">
         <v>12</v>
@@ -1974,10 +1976,10 @@
         <v>46325</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C69" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D69" t="s">
         <v>12</v>
@@ -1988,10 +1990,10 @@
         <v>46308</v>
       </c>
       <c r="B70" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C70" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D70" t="s">
         <v>12</v>
@@ -2002,7 +2004,7 @@
         <v>46305</v>
       </c>
       <c r="B71" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -2016,10 +2018,10 @@
         <v>46330</v>
       </c>
       <c r="B72" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C72" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D72" t="s">
         <v>12</v>
@@ -2030,10 +2032,10 @@
         <v>46310</v>
       </c>
       <c r="B73" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C73" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D73" t="s">
         <v>6</v>
@@ -2044,10 +2046,10 @@
         <v>46371</v>
       </c>
       <c r="B74" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C74" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D74" t="s">
         <v>6</v>
@@ -2058,10 +2060,10 @@
         <v>46376</v>
       </c>
       <c r="B75" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C75" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D75" t="s">
         <v>6</v>
@@ -2072,10 +2074,10 @@
         <v>46376</v>
       </c>
       <c r="B76" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D76" t="s">
         <v>6</v>
@@ -2086,10 +2088,10 @@
         <v>46341</v>
       </c>
       <c r="B77" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C77" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D77" t="s">
         <v>6</v>
@@ -2100,10 +2102,10 @@
         <v>46320</v>
       </c>
       <c r="B78" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C78" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D78" t="s">
         <v>6</v>
@@ -2114,7 +2116,7 @@
         <v>46317</v>
       </c>
       <c r="B79" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D79" t="s">
         <v>9</v>
@@ -2125,7 +2127,10 @@
         <v>46302</v>
       </c>
       <c r="B80" t="s">
-        <v>117</v>
+        <v>113</v>
+      </c>
+      <c r="C80" t="s">
+        <v>5</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
@@ -2136,7 +2141,7 @@
         <v>46295</v>
       </c>
       <c r="B81" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
@@ -2150,7 +2155,7 @@
         <v>46315</v>
       </c>
       <c r="B82" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
@@ -2161,7 +2166,7 @@
         <v>46302</v>
       </c>
       <c r="B83" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D83" t="s">
         <v>9</v>
@@ -2172,7 +2177,7 @@
         <v>46310</v>
       </c>
       <c r="B84" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D84" t="s">
         <v>9</v>
@@ -2183,7 +2188,7 @@
         <v>46320</v>
       </c>
       <c r="B85" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D85" t="s">
         <v>9</v>
@@ -2194,7 +2199,7 @@
         <v>46323</v>
       </c>
       <c r="B86" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
@@ -2208,7 +2213,7 @@
         <v>46300</v>
       </c>
       <c r="B87" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D87" t="s">
         <v>12</v>
@@ -2219,7 +2224,7 @@
         <v>46305</v>
       </c>
       <c r="B88" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D88" t="s">
         <v>12</v>
@@ -2230,7 +2235,7 @@
         <v>46295</v>
       </c>
       <c r="B89" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D89" t="s">
         <v>12</v>
@@ -2241,7 +2246,7 @@
         <v>46305</v>
       </c>
       <c r="B90" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D90" t="s">
         <v>12</v>
@@ -2252,7 +2257,7 @@
         <v>46320</v>
       </c>
       <c r="B91" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D91" t="s">
         <v>12</v>
@@ -2263,7 +2268,7 @@
         <v>46301</v>
       </c>
       <c r="B92" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
@@ -2277,10 +2282,10 @@
         <v>46320</v>
       </c>
       <c r="B93" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C93" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D93" t="s">
         <v>12</v>
@@ -2291,10 +2296,10 @@
         <v>46325</v>
       </c>
       <c r="B94" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C94" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D94" t="s">
         <v>12</v>
@@ -2305,10 +2310,10 @@
         <v>46331</v>
       </c>
       <c r="B95" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D95" t="s">
         <v>12</v>
@@ -2319,7 +2324,10 @@
         <v>46300</v>
       </c>
       <c r="B96" t="s">
-        <v>134</v>
+        <v>130</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
       </c>
       <c r="D96" t="s">
         <v>9</v>
@@ -2330,10 +2338,10 @@
         <v>46315</v>
       </c>
       <c r="B97" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C97" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
@@ -2344,10 +2352,10 @@
         <v>46314</v>
       </c>
       <c r="B98" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C98" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D98" t="s">
         <v>9</v>
@@ -2358,7 +2366,7 @@
         <v>46315</v>
       </c>
       <c r="B99" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
@@ -2366,10 +2374,13 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>46290</v>
+        <v>46310</v>
       </c>
       <c r="B100" t="s">
-        <v>138</v>
+        <v>134</v>
+      </c>
+      <c r="C100" t="s">
+        <v>5</v>
       </c>
       <c r="D100" t="s">
         <v>6</v>
@@ -2380,7 +2391,7 @@
         <v>46305</v>
       </c>
       <c r="B101" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D101" t="s">
         <v>6</v>
@@ -2391,7 +2402,7 @@
         <v>46295</v>
       </c>
       <c r="B102" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D102" t="s">
         <v>6</v>
@@ -2402,7 +2413,7 @@
         <v>46326</v>
       </c>
       <c r="B103" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D103" t="s">
         <v>6</v>
@@ -2413,7 +2424,7 @@
         <v>46300</v>
       </c>
       <c r="B104" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C104" t="s">
         <v>5</v>
@@ -2427,7 +2438,7 @@
         <v>46300</v>
       </c>
       <c r="B105" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C105" t="s">
         <v>5</v>
@@ -2441,7 +2452,7 @@
         <v>46356</v>
       </c>
       <c r="B106" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D106" t="s">
         <v>12</v>
@@ -2452,7 +2463,7 @@
         <v>46370</v>
       </c>
       <c r="B107" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D107" t="s">
         <v>12</v>
@@ -2462,242 +2473,248 @@
       <c r="A108" s="2">
         <v>46323</v>
       </c>
-      <c r="B108" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>174</v>
+      <c r="B108" t="s">
+        <v>142</v>
+      </c>
+      <c r="C108" t="s">
+        <v>170</v>
       </c>
       <c r="D108" t="s">
         <v>6</v>
       </c>
-      <c r="E108" s="5"/>
-      <c r="F108" s="6"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="5"/>
     </row>
     <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>46310</v>
       </c>
-      <c r="B109" s="4" t="s">
-        <v>147</v>
+      <c r="B109" t="s">
+        <v>143</v>
       </c>
       <c r="D109" t="s">
         <v>6</v>
       </c>
-      <c r="E109" s="7"/>
-      <c r="F109" s="5"/>
-      <c r="G109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="5"/>
     </row>
     <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>46325</v>
       </c>
-      <c r="B110" s="4" t="s">
-        <v>148</v>
+      <c r="B110" t="s">
+        <v>144</v>
       </c>
       <c r="C110" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D110" t="s">
         <v>6</v>
       </c>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
-      <c r="G110" s="6"/>
-    </row>
-    <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="5"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>46309</v>
       </c>
-      <c r="B111" s="8" t="s">
-        <v>149</v>
+      <c r="B111" t="s">
+        <v>145</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
       </c>
       <c r="D111" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>46311</v>
       </c>
-      <c r="B112" s="8" t="s">
-        <v>150</v>
+      <c r="B112" t="s">
+        <v>146</v>
       </c>
       <c r="D112" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>46321</v>
       </c>
-      <c r="B113" s="8" t="s">
-        <v>151</v>
+      <c r="B113" t="s">
+        <v>147</v>
       </c>
       <c r="D113" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>46313</v>
       </c>
-      <c r="B114" s="8" t="s">
-        <v>152</v>
+      <c r="B114" t="s">
+        <v>148</v>
       </c>
       <c r="D114" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>46311</v>
       </c>
-      <c r="B115" s="8" t="s">
-        <v>153</v>
+      <c r="B115" t="s">
+        <v>149</v>
       </c>
       <c r="D115" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>46312</v>
       </c>
-      <c r="B116" s="8" t="s">
-        <v>154</v>
+      <c r="B116" t="s">
+        <v>150</v>
       </c>
       <c r="D116" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>46312</v>
       </c>
-      <c r="B117" s="8" t="s">
-        <v>155</v>
+      <c r="B117" t="s">
+        <v>151</v>
       </c>
       <c r="D117" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>46312</v>
       </c>
-      <c r="B118" s="8" t="s">
-        <v>156</v>
+      <c r="B118" t="s">
+        <v>152</v>
       </c>
       <c r="D118" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>46310</v>
       </c>
-      <c r="B119" s="8" t="s">
-        <v>157</v>
+      <c r="B119" t="s">
+        <v>153</v>
       </c>
       <c r="D119" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>46314</v>
       </c>
-      <c r="B120" s="8" t="s">
-        <v>158</v>
+      <c r="B120" t="s">
+        <v>154</v>
       </c>
       <c r="D120" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>46310</v>
       </c>
-      <c r="B121" s="8" t="s">
-        <v>159</v>
+      <c r="B121" t="s">
+        <v>155</v>
+      </c>
+      <c r="C121" t="s">
+        <v>5</v>
       </c>
       <c r="D121" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>46320</v>
       </c>
-      <c r="B122" s="8" t="s">
-        <v>160</v>
+      <c r="B122" t="s">
+        <v>156</v>
       </c>
       <c r="D122" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>46323</v>
       </c>
-      <c r="B123" s="8" t="s">
-        <v>161</v>
+      <c r="B123" t="s">
+        <v>157</v>
       </c>
       <c r="D123" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>46332</v>
       </c>
-      <c r="B124" s="8" t="s">
-        <v>162</v>
+      <c r="B124" t="s">
+        <v>158</v>
       </c>
       <c r="D124" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>46337</v>
       </c>
-      <c r="B125" s="8" t="s">
-        <v>163</v>
+      <c r="B125" t="s">
+        <v>159</v>
       </c>
       <c r="D125" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>46325</v>
       </c>
-      <c r="B126" s="8" t="s">
-        <v>164</v>
+      <c r="B126" t="s">
+        <v>160</v>
       </c>
       <c r="D126" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>46312</v>
       </c>
-      <c r="B127" s="8" t="s">
-        <v>166</v>
+      <c r="B127" t="s">
+        <v>162</v>
       </c>
       <c r="D127" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>46313</v>
       </c>
-      <c r="B128" s="8" t="s">
-        <v>167</v>
+      <c r="B128" t="s">
+        <v>163</v>
       </c>
       <c r="D128" t="s">
         <v>6</v>
@@ -2707,8 +2724,8 @@
       <c r="A129" s="2">
         <v>46312</v>
       </c>
-      <c r="B129" s="9" t="s">
-        <v>173</v>
+      <c r="B129" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="D129" t="s">
         <v>6</v>
@@ -2718,8 +2735,8 @@
       <c r="A130" s="2">
         <v>46318</v>
       </c>
-      <c r="B130" s="9" t="s">
-        <v>172</v>
+      <c r="B130" s="7" t="s">
+        <v>168</v>
       </c>
       <c r="D130" t="s">
         <v>6</v>
@@ -2729,8 +2746,8 @@
       <c r="A131" s="2">
         <v>46321</v>
       </c>
-      <c r="B131" s="9" t="s">
-        <v>171</v>
+      <c r="B131" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="D131" t="s">
         <v>6</v>
@@ -2740,8 +2757,8 @@
       <c r="A132" s="2">
         <v>46336</v>
       </c>
-      <c r="B132" s="9" t="s">
-        <v>170</v>
+      <c r="B132" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="D132" t="s">
         <v>6</v>
@@ -2751,8 +2768,8 @@
       <c r="A133" s="2">
         <v>46318</v>
       </c>
-      <c r="B133" s="9" t="s">
-        <v>175</v>
+      <c r="B133" s="7" t="s">
+        <v>171</v>
       </c>
       <c r="D133" t="s">
         <v>6</v>
@@ -2762,8 +2779,8 @@
       <c r="A134" s="2">
         <v>46333</v>
       </c>
-      <c r="B134" s="9" t="s">
-        <v>179</v>
+      <c r="B134" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="D134" t="s">
         <v>6</v>
@@ -2773,8 +2790,8 @@
       <c r="A135" s="2">
         <v>46336</v>
       </c>
-      <c r="B135" s="9" t="s">
-        <v>180</v>
+      <c r="B135" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="D135" t="s">
         <v>6</v>
@@ -2784,8 +2801,8 @@
       <c r="A136" s="2">
         <v>46318</v>
       </c>
-      <c r="B136" s="9" t="s">
-        <v>181</v>
+      <c r="B136" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="D136" t="s">
         <v>6</v>
@@ -2795,8 +2812,8 @@
       <c r="A137" s="2">
         <v>46320</v>
       </c>
-      <c r="B137" s="9" t="s">
-        <v>183</v>
+      <c r="B137" s="7" t="s">
+        <v>179</v>
       </c>
       <c r="D137" t="s">
         <v>12</v>
@@ -2806,10 +2823,10 @@
       <c r="A138" s="2">
         <v>46317</v>
       </c>
-      <c r="B138" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C138" s="4"/>
+      <c r="B138" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C138" s="3"/>
       <c r="D138" t="s">
         <v>9</v>
       </c>
@@ -2818,10 +2835,10 @@
       <c r="A139" s="2">
         <v>46313</v>
       </c>
-      <c r="B139" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C139" s="4"/>
+      <c r="B139" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C139" s="3"/>
       <c r="D139" t="s">
         <v>9</v>
       </c>
@@ -2830,10 +2847,10 @@
       <c r="A140" s="2">
         <v>46317</v>
       </c>
-      <c r="B140" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C140" s="4"/>
+      <c r="B140" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C140" s="3"/>
       <c r="D140" t="s">
         <v>9</v>
       </c>
@@ -2842,10 +2859,10 @@
       <c r="A141" s="2">
         <v>46315</v>
       </c>
-      <c r="B141" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C141" s="4"/>
+      <c r="B141" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C141" s="3"/>
       <c r="D141" t="s">
         <v>9</v>
       </c>
@@ -2854,10 +2871,10 @@
       <c r="A142" s="2">
         <v>46320</v>
       </c>
-      <c r="B142" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C142" s="4"/>
+      <c r="B142" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C142" s="3"/>
       <c r="D142" t="s">
         <v>9</v>
       </c>
@@ -2866,10 +2883,10 @@
       <c r="A143" s="2">
         <v>46315</v>
       </c>
-      <c r="B143" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C143" s="4"/>
+      <c r="B143" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C143" s="3"/>
       <c r="D143" t="s">
         <v>9</v>
       </c>
@@ -2878,10 +2895,10 @@
       <c r="A144" s="2">
         <v>46336</v>
       </c>
-      <c r="B144" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="C144" s="10"/>
+      <c r="B144" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C144" s="8"/>
       <c r="D144" t="s">
         <v>9</v>
       </c>
@@ -2890,18 +2907,33 @@
       <c r="A145" s="2">
         <v>46326</v>
       </c>
-      <c r="B145" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="C145" s="10"/>
+      <c r="B145" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C145" s="8"/>
       <c r="D145" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A146" s="11"/>
-      <c r="B146" s="12"/>
-      <c r="C146" s="13"/>
+      <c r="A146" s="11">
+        <v>46341</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C146" s="10"/>
+      <c r="D146" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="2">
+        <v>46356</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>189</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D21">

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="886" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E14EB96-8EE4-46E5-8367-CDA1F68CD3F4}"/>
+  <xr:revisionPtr revIDLastSave="980" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF369D63-370A-4B21-9475-4FF826BDDDF4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="203">
   <si>
     <t>Date</t>
   </si>
@@ -167,15 +167,9 @@
     <t xml:space="preserve">CER to ESP RHS Foundation completion </t>
   </si>
   <si>
-    <t>Delayed -30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.10.26</t>
-  </si>
-  <si>
     <t xml:space="preserve">CER to ESP LHS Foundation completion </t>
   </si>
   <si>
-    <t>Delayed -30.06.26/15.07.26/30.07.26/14.08.26/05.09.26</t>
-  </si>
-  <si>
     <t xml:space="preserve">CER to Boiler Foundation completion </t>
   </si>
   <si>
@@ -215,15 +209,9 @@
     <t>ACC - Street 1 ATT</t>
   </si>
   <si>
-    <t>Delayed - 20.09.26</t>
-  </si>
-  <si>
     <t>ACC - Street 3 ATT</t>
   </si>
   <si>
-    <t>Delayed - 30.09.26</t>
-  </si>
-  <si>
     <t>ACC - Street 4 ATT</t>
   </si>
   <si>
@@ -233,9 +221,6 @@
     <t>ACC - Street 5 ATT</t>
   </si>
   <si>
-    <t>Delayed - 05.11.26</t>
-  </si>
-  <si>
     <t>ACC - Street 6 ATT</t>
   </si>
   <si>
@@ -254,9 +239,6 @@
     <t>MDBP motor trial</t>
   </si>
   <si>
-    <t>Delayed -17.10.26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Street 1 ACC erection completion </t>
   </si>
   <si>
@@ -329,9 +311,6 @@
     <t>3BB Board charging</t>
   </si>
   <si>
-    <t>Delayed - 16.09.26/30.09.26</t>
-  </si>
-  <si>
     <t>ST-2 charging</t>
   </si>
   <si>
@@ -344,9 +323,6 @@
     <t>Start of TG Lube oil flushing</t>
   </si>
   <si>
-    <t>Delayed - 05.10.26</t>
-  </si>
-  <si>
     <t>MS Line Hydro Test</t>
   </si>
   <si>
@@ -494,18 +470,12 @@
     <t>MOT Cleaning and Oil Filling</t>
   </si>
   <si>
-    <t>Starting Oil flushing (Supply &amp; Return oil lines flushing)</t>
-  </si>
-  <si>
     <t>Seal oil System Piping readiness for cardboard bursting</t>
   </si>
   <si>
     <t>Seal oil System Piping complete readiness (for flushing)</t>
   </si>
   <si>
-    <t>MDBFP Lube oil flushing</t>
-  </si>
-  <si>
     <t>ECW Overhead Tank &amp; Piping readiness</t>
   </si>
   <si>
@@ -521,9 +491,6 @@
     <t>ACW Piping completion and load trial</t>
   </si>
   <si>
-    <t>Delayed - 10.09.26/20.09.26/30.09.26</t>
-  </si>
-  <si>
     <t>TDBP EOT Commissioning</t>
   </si>
   <si>
@@ -554,12 +521,6 @@
     <t>150 manpower by alternate agency M/s M&amp;S in Piping scope</t>
   </si>
   <si>
-    <t>Delayed -30.09.26</t>
-  </si>
-  <si>
-    <t>Delayed - 10.10.26</t>
-  </si>
-  <si>
     <t>Delayed - 30.09.26/10.10.26/15.10.26</t>
   </si>
   <si>
@@ -587,9 +548,6 @@
     <t>Approach to Boiler RHS from CR-11, 12 by </t>
   </si>
   <si>
-    <t>K row drain completion by </t>
-  </si>
-  <si>
     <t>ESP 3 F pass inlet area paving completion by (Last commitment - 19-09-26)</t>
   </si>
   <si>
@@ -618,6 +576,75 @@
   </si>
   <si>
     <t>Delayed - 30.08.26/30.09.26/15.10.26</t>
+  </si>
+  <si>
+    <t>Delayed - 20.09.26/15.10.26</t>
+  </si>
+  <si>
+    <t>Delayed - 25.10.26/15.11.26</t>
+  </si>
+  <si>
+    <t>Delayed - 10.09.26/20.09.26/30.09.26/15.10.26</t>
+  </si>
+  <si>
+    <t>Delayed</t>
+  </si>
+  <si>
+    <t>Delayed -20.10.26</t>
+  </si>
+  <si>
+    <t>Delayed-07.10.26</t>
+  </si>
+  <si>
+    <t>Delayed - 10.10.26/19.10.26</t>
+  </si>
+  <si>
+    <t>Start of MDBFP Lube oil flushing</t>
+  </si>
+  <si>
+    <t>Delayed - 22-10-26</t>
+  </si>
+  <si>
+    <t>Delayed - 22.10.26</t>
+  </si>
+  <si>
+    <t>Delayed - 23-10-26</t>
+  </si>
+  <si>
+    <t>Delayed - 10-11-26</t>
+  </si>
+  <si>
+    <t>Delayed - 17-10-26</t>
+  </si>
+  <si>
+    <t>Delayed - 18-10-26</t>
+  </si>
+  <si>
+    <t>Delayed - 26-10-26</t>
+  </si>
+  <si>
+    <t>Delayed - 25.10.26/30.10.26</t>
+  </si>
+  <si>
+    <t>Delayed - 30-09-26</t>
+  </si>
+  <si>
+    <t>Delayed - 30.09.26/25.10.26/05.11.26</t>
+  </si>
+  <si>
+    <t>Delayed - 05.11.26/15.11.26/25.11.26</t>
+  </si>
+  <si>
+    <t>Delayed - 05.12.26</t>
+  </si>
+  <si>
+    <t>Delayed - 29.12.26</t>
+  </si>
+  <si>
+    <t>Delayed -17.10.26/25.10.26</t>
+  </si>
+  <si>
+    <t>Delayed -30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.10.26/25.10.26</t>
   </si>
 </sst>
 </file>
@@ -1052,16 +1079,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G147"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G145"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1075,7 +1102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>46259</v>
       </c>
@@ -1089,7 +1116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>46237</v>
       </c>
@@ -1103,7 +1130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>46244</v>
       </c>
@@ -1117,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>46251</v>
       </c>
@@ -1131,7 +1158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>46280</v>
       </c>
@@ -1145,7 +1172,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>46269</v>
       </c>
@@ -1159,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>46251</v>
       </c>
@@ -1173,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>46341</v>
       </c>
@@ -1187,7 +1214,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>46325</v>
       </c>
@@ -1195,13 +1222,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>46290</v>
       </c>
@@ -1215,7 +1242,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>46305</v>
       </c>
@@ -1229,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>46356</v>
       </c>
@@ -1243,26 +1270,26 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>46280</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -1271,7 +1298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>46366</v>
       </c>
@@ -1285,7 +1312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>46381</v>
       </c>
@@ -1299,7 +1326,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>46402</v>
       </c>
@@ -1313,7 +1340,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>46444</v>
       </c>
@@ -1327,7 +1354,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>46456</v>
       </c>
@@ -1341,7 +1368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>46461</v>
       </c>
@@ -1352,7 +1379,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46254</v>
       </c>
@@ -1366,7 +1393,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>46371</v>
       </c>
@@ -1380,7 +1407,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>46336</v>
       </c>
@@ -1394,7 +1421,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>46302</v>
       </c>
@@ -1408,7 +1435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>46402</v>
       </c>
@@ -1419,40 +1446,40 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
-        <v>46320</v>
+        <v>46326</v>
       </c>
       <c r="B27" t="s">
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>202</v>
       </c>
       <c r="D27" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <v>46320</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D28" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>46270</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -1461,26 +1488,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>46326</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>46275</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -1489,26 +1516,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>46326</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D32" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>46301</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -1517,12 +1544,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>46295</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1531,26 +1558,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>46290</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>46254</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1559,12 +1586,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>46272</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1573,12 +1600,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>46285</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -1587,151 +1614,157 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>46300</v>
       </c>
       <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" t="s">
+        <v>180</v>
+      </c>
+      <c r="D40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" s="2">
+        <v>46338</v>
+      </c>
+      <c r="B41" t="s">
         <v>57</v>
       </c>
-      <c r="C39" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>46310</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="C41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" s="2">
+        <v>46354</v>
+      </c>
+      <c r="B42" t="s">
         <v>58</v>
       </c>
-      <c r="C40" t="s">
-        <v>59</v>
-      </c>
-      <c r="D40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>46320</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="C42" t="s">
+        <v>181</v>
+      </c>
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" s="2">
+        <v>46362</v>
+      </c>
+      <c r="B43" t="s">
         <v>60</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C43" t="s">
+        <v>198</v>
+      </c>
+      <c r="D43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" s="2">
+        <v>46377</v>
+      </c>
+      <c r="B44" t="s">
         <v>61</v>
       </c>
-      <c r="D41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>46331</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="C44" t="s">
+        <v>199</v>
+      </c>
+      <c r="D44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" s="2">
+        <v>46391</v>
+      </c>
+      <c r="B45" t="s">
         <v>62</v>
       </c>
-      <c r="C42" t="s">
-        <v>63</v>
-      </c>
-      <c r="D42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>46341</v>
-      </c>
-      <c r="B43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" t="s">
-        <v>65</v>
-      </c>
-      <c r="D43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>46361</v>
-      </c>
-      <c r="B44" t="s">
-        <v>66</v>
-      </c>
-      <c r="D44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>46385</v>
-      </c>
-      <c r="B45" t="s">
-        <v>67</v>
+      <c r="C45" t="s">
+        <v>200</v>
       </c>
       <c r="D45" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>46401</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D46" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
         <v>46382</v>
       </c>
       <c r="B47" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D47" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>46371</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D48" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
-        <v>46320</v>
+        <v>46336</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>46265</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -1740,12 +1773,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>46290</v>
       </c>
       <c r="B51" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -1754,81 +1787,81 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
-        <v>46310</v>
+        <v>46320</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C52" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D52" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>46326</v>
       </c>
       <c r="B53" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D53" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>46326</v>
       </c>
       <c r="B54" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D54" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
         <v>46346</v>
       </c>
       <c r="B55" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D55" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
         <v>46366</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D56" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>46385</v>
       </c>
       <c r="B57" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D57" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>46285</v>
       </c>
       <c r="B58" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -1837,62 +1870,68 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
         <v>46320</v>
       </c>
       <c r="B59" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C59" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D59" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>46326</v>
       </c>
       <c r="B60" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D60" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
-        <v>46315</v>
+        <v>46341</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
+        <v>78</v>
+      </c>
+      <c r="C61" t="s">
+        <v>159</v>
       </c>
       <c r="D61" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
-        <v>46326</v>
+        <v>46351</v>
       </c>
       <c r="B62" t="s">
-        <v>85</v>
+        <v>79</v>
+      </c>
+      <c r="C62" t="s">
+        <v>59</v>
       </c>
       <c r="D62" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
         <v>46277</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -1901,12 +1940,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
         <v>46308</v>
       </c>
       <c r="B64" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -1915,12 +1954,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>46275</v>
       </c>
       <c r="B65" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -1929,12 +1968,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>46265</v>
       </c>
       <c r="B66" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -1943,68 +1982,68 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>46320</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D67" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>46331</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C68" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D68" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>46325</v>
       </c>
       <c r="B69" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C69" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D69" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
-        <v>46308</v>
+        <v>46319</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C70" t="s">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="D70" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
         <v>46305</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -2013,121 +2052,124 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
         <v>46330</v>
       </c>
       <c r="B72" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C72" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D72" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
-        <v>46310</v>
+        <v>46319</v>
       </c>
       <c r="B73" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C73" t="s">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="D73" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>46371</v>
       </c>
       <c r="B74" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C74" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D74" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
         <v>46376</v>
       </c>
       <c r="B75" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C75" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D75" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
         <v>46376</v>
       </c>
       <c r="B76" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D76" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
         <v>46341</v>
       </c>
       <c r="B77" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C77" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D77" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>46320</v>
       </c>
       <c r="B78" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C78" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D78" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
-        <v>46317</v>
+        <v>46336</v>
       </c>
       <c r="B79" t="s">
-        <v>112</v>
+        <v>104</v>
+      </c>
+      <c r="C79" t="s">
+        <v>183</v>
       </c>
       <c r="D79" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>46302</v>
       </c>
       <c r="B80" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C80" t="s">
         <v>5</v>
@@ -2136,12 +2178,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>46295</v>
       </c>
       <c r="B81" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
@@ -2150,56 +2192,62 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
-        <v>46315</v>
+        <v>46336</v>
       </c>
       <c r="B82" t="s">
-        <v>115</v>
+        <v>107</v>
+      </c>
+      <c r="C82" t="s">
+        <v>184</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
         <v>46302</v>
       </c>
       <c r="B83" t="s">
-        <v>116</v>
+        <v>108</v>
+      </c>
+      <c r="C83" t="s">
+        <v>185</v>
       </c>
       <c r="D83" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>46310</v>
       </c>
       <c r="B84" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D84" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>46320</v>
       </c>
       <c r="B85" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D85" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>46323</v>
       </c>
       <c r="B86" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
@@ -2208,67 +2256,70 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>46300</v>
       </c>
       <c r="B87" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D87" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>46305</v>
       </c>
       <c r="B88" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D88" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
-        <v>46295</v>
+        <v>46325</v>
       </c>
       <c r="B89" t="s">
-        <v>122</v>
+        <v>114</v>
+      </c>
+      <c r="C89" t="s">
+        <v>196</v>
       </c>
       <c r="D89" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>46305</v>
       </c>
       <c r="B90" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D90" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>46320</v>
       </c>
       <c r="B91" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D91" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>46301</v>
       </c>
       <c r="B92" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
@@ -2277,54 +2328,54 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>46320</v>
       </c>
       <c r="B93" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C93" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>46325</v>
       </c>
       <c r="B94" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C94" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D94" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>46331</v>
       </c>
       <c r="B95" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C95" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D95" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>46300</v>
       </c>
       <c r="B96" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C96" t="s">
         <v>5</v>
@@ -2333,51 +2384,54 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>46315</v>
       </c>
       <c r="B97" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C97" t="s">
-        <v>173</v>
+        <v>5</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
-        <v>46314</v>
+        <v>46322</v>
       </c>
       <c r="B98" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C98" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D98" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>46315</v>
       </c>
       <c r="B99" t="s">
-        <v>133</v>
+        <v>125</v>
+      </c>
+      <c r="C99" t="s">
+        <v>5</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
         <v>46310</v>
       </c>
       <c r="B100" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C100" t="s">
         <v>5</v>
@@ -2386,45 +2440,45 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>46305</v>
       </c>
       <c r="B101" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D101" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>46295</v>
       </c>
       <c r="B102" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D102" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
         <v>46326</v>
       </c>
       <c r="B103" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D103" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>46300</v>
       </c>
       <c r="B104" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C104" t="s">
         <v>5</v>
@@ -2433,12 +2487,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
         <v>46300</v>
       </c>
       <c r="B105" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C105" t="s">
         <v>5</v>
@@ -2447,37 +2501,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>46356</v>
       </c>
       <c r="B106" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D106" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>46370</v>
       </c>
       <c r="B107" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D107" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>46323</v>
       </c>
       <c r="B108" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C108" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D108" t="s">
         <v>6</v>
@@ -2485,12 +2539,15 @@
       <c r="E108" s="4"/>
       <c r="F108" s="5"/>
     </row>
-    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
-        <v>46310</v>
+        <v>46325</v>
       </c>
       <c r="B109" t="s">
-        <v>143</v>
+        <v>135</v>
+      </c>
+      <c r="C109" t="s">
+        <v>119</v>
       </c>
       <c r="D109" t="s">
         <v>6</v>
@@ -2499,15 +2556,15 @@
       <c r="F109" s="4"/>
       <c r="G109" s="5"/>
     </row>
-    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="B110" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C110" t="s">
-        <v>63</v>
+        <v>195</v>
       </c>
       <c r="D110" t="s">
         <v>6</v>
@@ -2516,12 +2573,12 @@
       <c r="F110" s="4"/>
       <c r="G110" s="5"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
         <v>46309</v>
       </c>
       <c r="B111" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C111" t="s">
         <v>5</v>
@@ -2530,409 +2587,445 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
         <v>46311</v>
       </c>
       <c r="B112" t="s">
-        <v>146</v>
+        <v>138</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
       </c>
       <c r="D112" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>46321</v>
       </c>
       <c r="B113" t="s">
-        <v>147</v>
+        <v>139</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5</v>
       </c>
       <c r="D113" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>46313</v>
       </c>
       <c r="B114" t="s">
-        <v>148</v>
+        <v>140</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
       </c>
       <c r="D114" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>46311</v>
       </c>
       <c r="B115" t="s">
-        <v>149</v>
+        <v>141</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
       </c>
       <c r="D115" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>46312</v>
       </c>
       <c r="B116" t="s">
-        <v>150</v>
+        <v>142</v>
+      </c>
+      <c r="C116" t="s">
+        <v>5</v>
       </c>
       <c r="D116" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>46312</v>
       </c>
       <c r="B117" t="s">
+        <v>143</v>
+      </c>
+      <c r="C117" t="s">
+        <v>5</v>
+      </c>
+      <c r="D117" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A118" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B118" t="s">
+        <v>144</v>
+      </c>
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A119" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B119" t="s">
+        <v>145</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A120" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B120" t="s">
+        <v>187</v>
+      </c>
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A121" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B121" t="s">
+        <v>146</v>
+      </c>
+      <c r="D121" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A122" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B122" t="s">
+        <v>147</v>
+      </c>
+      <c r="D122" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A123" s="2">
+        <v>46332</v>
+      </c>
+      <c r="B123" t="s">
+        <v>148</v>
+      </c>
+      <c r="D123" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A124" s="2">
+        <v>46337</v>
+      </c>
+      <c r="B124" t="s">
+        <v>149</v>
+      </c>
+      <c r="D124" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A125" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B125" t="s">
+        <v>150</v>
+      </c>
+      <c r="D125" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A126" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B126" t="s">
         <v>151</v>
       </c>
-      <c r="D117" t="s">
+      <c r="C126" t="s">
+        <v>192</v>
+      </c>
+      <c r="D126" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A127" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B127" t="s">
+        <v>152</v>
+      </c>
+      <c r="C127" t="s">
+        <v>193</v>
+      </c>
+      <c r="D127" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A128" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A129" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C129" t="s">
+        <v>190</v>
+      </c>
+      <c r="D129" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A130" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C130" t="s">
+        <v>194</v>
+      </c>
+      <c r="D130" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A131" s="2">
+        <v>46351</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C131" t="s">
+        <v>191</v>
+      </c>
+      <c r="D131" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A132" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C132" t="s">
+        <v>190</v>
+      </c>
+      <c r="D132" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A133" s="2">
+        <v>46333</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D133" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A134" s="2">
+        <v>46336</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D134" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A135" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B135" s="7" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
-        <v>46312</v>
-      </c>
-      <c r="B118" t="s">
-        <v>152</v>
-      </c>
-      <c r="D118" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
-        <v>46310</v>
-      </c>
-      <c r="B119" t="s">
-        <v>153</v>
-      </c>
-      <c r="D119" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
-        <v>46314</v>
-      </c>
-      <c r="B120" t="s">
-        <v>154</v>
-      </c>
-      <c r="D120" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
-        <v>46310</v>
-      </c>
-      <c r="B121" t="s">
-        <v>155</v>
-      </c>
-      <c r="C121" t="s">
-        <v>5</v>
-      </c>
-      <c r="D121" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
+      <c r="C135" t="s">
+        <v>5</v>
+      </c>
+      <c r="D135" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A136" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C136" t="s">
+        <v>59</v>
+      </c>
+      <c r="D136" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A137" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A138" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A139" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A140" s="2">
         <v>46320</v>
       </c>
-      <c r="B122" t="s">
-        <v>156</v>
-      </c>
-      <c r="D122" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
-        <v>46323</v>
-      </c>
-      <c r="B123" t="s">
-        <v>157</v>
-      </c>
-      <c r="D123" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
-        <v>46332</v>
-      </c>
-      <c r="B124" t="s">
-        <v>158</v>
-      </c>
-      <c r="D124" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
-        <v>46337</v>
-      </c>
-      <c r="B125" t="s">
-        <v>159</v>
-      </c>
-      <c r="D125" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
-        <v>46325</v>
-      </c>
-      <c r="B126" t="s">
-        <v>160</v>
-      </c>
-      <c r="D126" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
-        <v>46312</v>
-      </c>
-      <c r="B127" t="s">
-        <v>162</v>
-      </c>
-      <c r="D127" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
-        <v>46313</v>
-      </c>
-      <c r="B128" t="s">
-        <v>163</v>
-      </c>
-      <c r="D128" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
-        <v>46312</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="D129" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
-        <v>46318</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D130" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
-        <v>46321</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D131" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
-        <v>46336</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D132" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
-        <v>46318</v>
-      </c>
-      <c r="B133" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="D133" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
-        <v>46333</v>
-      </c>
-      <c r="B134" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D134" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
-        <v>46336</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D135" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
-        <v>46318</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D136" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
-        <v>46320</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D137" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
-        <v>46317</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C138" s="3"/>
-      <c r="D138" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
-        <v>46313</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C139" s="3"/>
-      <c r="D139" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
-        <v>46317</v>
-      </c>
       <c r="B140" s="7" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="C140" s="3"/>
       <c r="D140" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A141" s="2">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C141" s="3"/>
+        <v>171</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>159</v>
+      </c>
       <c r="D141" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A142" s="2">
-        <v>46320</v>
+        <v>46336</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C142" s="3"/>
+        <v>172</v>
+      </c>
+      <c r="C142" s="8"/>
       <c r="D142" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A143" s="2">
-        <v>46315</v>
+        <v>46326</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C143" s="3"/>
+        <v>173</v>
+      </c>
+      <c r="C143" s="8"/>
       <c r="D143" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A144" s="2">
-        <v>46336</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C144" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="A144" s="11">
+        <v>46341</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C144" s="10"/>
       <c r="D144" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A145" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C145" s="8"/>
-      <c r="D145" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A146" s="11">
-        <v>46341</v>
-      </c>
-      <c r="B146" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C146" s="10"/>
-      <c r="D146" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
-        <v>46356</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="980" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF369D63-370A-4B21-9475-4FF826BDDDF4}"/>
+  <xr:revisionPtr revIDLastSave="982" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{297B5022-EBC4-41D9-A871-BB252B981F56}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="202">
   <si>
     <t>Date</t>
   </si>
@@ -591,9 +591,6 @@
   </si>
   <si>
     <t>Delayed -20.10.26</t>
-  </si>
-  <si>
-    <t>Delayed-07.10.26</t>
   </si>
   <si>
     <t>Delayed - 10.10.26/19.10.26</t>
@@ -1454,7 +1451,7 @@
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D27" t="s">
         <v>9</v>
@@ -1650,7 +1647,7 @@
         <v>57</v>
       </c>
       <c r="C41" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D41" t="s">
         <v>6</v>
@@ -1678,7 +1675,7 @@
         <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D43" t="s">
         <v>6</v>
@@ -1692,7 +1689,7 @@
         <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D44" t="s">
         <v>6</v>
@@ -1706,7 +1703,7 @@
         <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D45" t="s">
         <v>6</v>
@@ -1753,7 +1750,7 @@
         <v>66</v>
       </c>
       <c r="C49" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
@@ -2208,13 +2205,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
-        <v>46302</v>
+        <v>46319</v>
       </c>
       <c r="B83" t="s">
         <v>108</v>
       </c>
       <c r="C83" t="s">
-        <v>185</v>
+        <v>5</v>
       </c>
       <c r="D83" t="s">
         <v>9</v>
@@ -2286,7 +2283,7 @@
         <v>114</v>
       </c>
       <c r="C89" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D89" t="s">
         <v>12</v>
@@ -2406,7 +2403,7 @@
         <v>124</v>
       </c>
       <c r="C98" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D98" t="s">
         <v>9</v>
@@ -2564,7 +2561,7 @@
         <v>136</v>
       </c>
       <c r="C110" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D110" t="s">
         <v>6</v>
@@ -2704,7 +2701,7 @@
         <v>46310</v>
       </c>
       <c r="B120" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C120" t="s">
         <v>5</v>
@@ -2776,7 +2773,7 @@
         <v>151</v>
       </c>
       <c r="C126" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D126" t="s">
         <v>6</v>
@@ -2790,7 +2787,7 @@
         <v>152</v>
       </c>
       <c r="C127" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D127" t="s">
         <v>6</v>
@@ -2818,7 +2815,7 @@
         <v>157</v>
       </c>
       <c r="C129" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D129" t="s">
         <v>6</v>
@@ -2832,7 +2829,7 @@
         <v>156</v>
       </c>
       <c r="C130" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D130" t="s">
         <v>6</v>
@@ -2846,7 +2843,7 @@
         <v>155</v>
       </c>
       <c r="C131" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D131" t="s">
         <v>6</v>
@@ -2860,7 +2857,7 @@
         <v>160</v>
       </c>
       <c r="C132" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D132" t="s">
         <v>6</v>
@@ -2924,7 +2921,7 @@
         <v>167</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D137" t="s">
         <v>9</v>
@@ -2952,7 +2949,7 @@
         <v>169</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D139" t="s">
         <v>9</v>

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="982" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{297B5022-EBC4-41D9-A871-BB252B981F56}"/>
+  <xr:revisionPtr revIDLastSave="1010" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DF330F2-A9E3-4452-994F-242BEA97868A}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="210">
   <si>
     <t>Date</t>
   </si>
@@ -642,6 +642,31 @@
   </si>
   <si>
     <t>Delayed -30.06.26/15.07.26/30.07.26/10.08.26/31.08.26/10.10.26/25.10.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+Boiler LHS MS line completion upto MSV</t>
+  </si>
+  <si>
+    <t>Boiler RHS MS line completion upto MSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erection oil flushing completion </t>
+  </si>
+  <si>
+    <t>Turbine zero position</t>
+  </si>
+  <si>
+    <t>Delayed - 14.12.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotbox works completion </t>
+  </si>
+  <si>
+    <t>Delayed - 20.10.26/24.10.26</t>
+  </si>
+  <si>
+    <t>Delayed - 15.10.26/30.10.26</t>
   </si>
 </sst>
 </file>
@@ -743,7 +768,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -773,6 +798,12 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1076,16 +1107,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G145"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:G150"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="90.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1099,7 +1130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46259</v>
       </c>
@@ -1113,7 +1144,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46237</v>
       </c>
@@ -1127,7 +1158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46244</v>
       </c>
@@ -1141,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46251</v>
       </c>
@@ -1155,7 +1186,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46280</v>
       </c>
@@ -1169,7 +1200,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46269</v>
       </c>
@@ -1183,7 +1214,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46251</v>
       </c>
@@ -1197,7 +1228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46341</v>
       </c>
@@ -1211,7 +1242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46325</v>
       </c>
@@ -1225,7 +1256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46290</v>
       </c>
@@ -1239,7 +1270,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46305</v>
       </c>
@@ -1253,7 +1284,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46356</v>
       </c>
@@ -1267,7 +1298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>46319</v>
       </c>
@@ -1281,7 +1312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>46280</v>
       </c>
@@ -1295,7 +1326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>46366</v>
       </c>
@@ -1309,7 +1340,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>46381</v>
       </c>
@@ -1323,7 +1354,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>46402</v>
       </c>
@@ -1337,7 +1368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>46444</v>
       </c>
@@ -1351,7 +1382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>46456</v>
       </c>
@@ -1365,7 +1396,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46461</v>
       </c>
@@ -1376,7 +1407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46254</v>
       </c>
@@ -1390,7 +1421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>46371</v>
       </c>
@@ -1404,7 +1435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>46336</v>
       </c>
@@ -1418,7 +1449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>46302</v>
       </c>
@@ -1432,7 +1463,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>46402</v>
       </c>
@@ -1443,7 +1474,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>46326</v>
       </c>
@@ -1457,7 +1488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>46320</v>
       </c>
@@ -1471,7 +1502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>46270</v>
       </c>
@@ -1485,7 +1516,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>46326</v>
       </c>
@@ -1499,7 +1530,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>46275</v>
       </c>
@@ -1513,7 +1544,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>46326</v>
       </c>
@@ -1527,7 +1558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>46301</v>
       </c>
@@ -1541,7 +1572,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>46295</v>
       </c>
@@ -1555,7 +1586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>46290</v>
       </c>
@@ -1569,7 +1600,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>46254</v>
       </c>
@@ -1583,7 +1614,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>46272</v>
       </c>
@@ -1597,7 +1628,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>46285</v>
       </c>
@@ -1611,7 +1642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>46300</v>
       </c>
@@ -1625,7 +1656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>46320</v>
       </c>
@@ -1639,7 +1670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>46338</v>
       </c>
@@ -1653,7 +1684,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>46354</v>
       </c>
@@ -1667,7 +1698,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>46362</v>
       </c>
@@ -1681,7 +1712,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>46377</v>
       </c>
@@ -1695,7 +1726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>46391</v>
       </c>
@@ -1709,7 +1740,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46401</v>
       </c>
@@ -1720,7 +1751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46382</v>
       </c>
@@ -1731,7 +1762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>46371</v>
       </c>
@@ -1742,7 +1773,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>46336</v>
       </c>
@@ -1756,7 +1787,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>46265</v>
       </c>
@@ -1770,7 +1801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>46290</v>
       </c>
@@ -1784,7 +1815,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>46320</v>
       </c>
@@ -1798,7 +1829,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>46326</v>
       </c>
@@ -1809,7 +1840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>46326</v>
       </c>
@@ -1820,7 +1851,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>46346</v>
       </c>
@@ -1831,7 +1862,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>46366</v>
       </c>
@@ -1842,7 +1873,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>46385</v>
       </c>
@@ -1853,7 +1884,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>46285</v>
       </c>
@@ -1867,7 +1898,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>46320</v>
       </c>
@@ -1881,7 +1912,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>46326</v>
       </c>
@@ -1895,7 +1926,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>46341</v>
       </c>
@@ -1909,7 +1940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>46351</v>
       </c>
@@ -1923,7 +1954,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>46277</v>
       </c>
@@ -1937,7 +1968,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>46308</v>
       </c>
@@ -1951,7 +1982,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>46275</v>
       </c>
@@ -1965,7 +1996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>46265</v>
       </c>
@@ -1979,7 +2010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>46320</v>
       </c>
@@ -1993,7 +2024,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>46331</v>
       </c>
@@ -2007,7 +2038,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>46325</v>
       </c>
@@ -2021,7 +2052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>46319</v>
       </c>
@@ -2035,7 +2066,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>46305</v>
       </c>
@@ -2049,7 +2080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>46330</v>
       </c>
@@ -2063,7 +2094,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>46319</v>
       </c>
@@ -2077,7 +2108,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>46371</v>
       </c>
@@ -2091,7 +2122,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>46376</v>
       </c>
@@ -2105,7 +2136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>46376</v>
       </c>
@@ -2119,7 +2150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>46341</v>
       </c>
@@ -2133,7 +2164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>46320</v>
       </c>
@@ -2147,7 +2178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>46336</v>
       </c>
@@ -2161,7 +2192,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>46302</v>
       </c>
@@ -2175,7 +2206,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>46295</v>
       </c>
@@ -2189,7 +2220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>46336</v>
       </c>
@@ -2203,7 +2234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>46319</v>
       </c>
@@ -2217,7 +2248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>46310</v>
       </c>
@@ -2228,7 +2259,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>46320</v>
       </c>
@@ -2239,7 +2270,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>46323</v>
       </c>
@@ -2253,7 +2284,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>46300</v>
       </c>
@@ -2264,7 +2295,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>46305</v>
       </c>
@@ -2275,7 +2306,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>46325</v>
       </c>
@@ -2289,7 +2320,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>46305</v>
       </c>
@@ -2300,7 +2331,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>46320</v>
       </c>
@@ -2311,7 +2342,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>46301</v>
       </c>
@@ -2325,7 +2356,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>46320</v>
       </c>
@@ -2339,7 +2370,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>46325</v>
       </c>
@@ -2353,7 +2384,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>46331</v>
       </c>
@@ -2367,7 +2398,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>46300</v>
       </c>
@@ -2381,7 +2412,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>46315</v>
       </c>
@@ -2395,7 +2426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>46322</v>
       </c>
@@ -2409,7 +2440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>46315</v>
       </c>
@@ -2423,7 +2454,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>46310</v>
       </c>
@@ -2437,7 +2468,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>46305</v>
       </c>
@@ -2448,7 +2479,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>46295</v>
       </c>
@@ -2459,7 +2490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>46326</v>
       </c>
@@ -2470,7 +2501,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>46300</v>
       </c>
@@ -2484,7 +2515,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>46300</v>
       </c>
@@ -2498,7 +2529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>46356</v>
       </c>
@@ -2509,26 +2540,29 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
-        <v>46370</v>
+        <v>46380</v>
       </c>
       <c r="B107" t="s">
         <v>133</v>
       </c>
+      <c r="C107" t="s">
+        <v>206</v>
+      </c>
       <c r="D107" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>46323</v>
+        <v>46331</v>
       </c>
       <c r="B108" t="s">
         <v>134</v>
       </c>
       <c r="C108" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="D108" t="s">
         <v>6</v>
@@ -2536,15 +2570,15 @@
       <c r="E108" s="4"/>
       <c r="F108" s="5"/>
     </row>
-    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>46325</v>
+        <v>46331</v>
       </c>
       <c r="B109" t="s">
         <v>135</v>
       </c>
       <c r="C109" t="s">
-        <v>119</v>
+        <v>209</v>
       </c>
       <c r="D109" t="s">
         <v>6</v>
@@ -2553,7 +2587,7 @@
       <c r="F109" s="4"/>
       <c r="G109" s="5"/>
     </row>
-    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>46332</v>
       </c>
@@ -2570,7 +2604,7 @@
       <c r="F110" s="4"/>
       <c r="G110" s="5"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>46309</v>
       </c>
@@ -2584,7 +2618,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>46311</v>
       </c>
@@ -2598,7 +2632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>46321</v>
       </c>
@@ -2612,7 +2646,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>46313</v>
       </c>
@@ -2626,7 +2660,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>46311</v>
       </c>
@@ -2640,7 +2674,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>46312</v>
       </c>
@@ -2654,7 +2688,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>46312</v>
       </c>
@@ -2668,7 +2702,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>46310</v>
       </c>
@@ -2682,7 +2716,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>46314</v>
       </c>
@@ -2696,7 +2730,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>46310</v>
       </c>
@@ -2710,7 +2744,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>46320</v>
       </c>
@@ -2721,7 +2755,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>46323</v>
       </c>
@@ -2732,7 +2766,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>46332</v>
       </c>
@@ -2743,7 +2777,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>46337</v>
       </c>
@@ -2754,7 +2788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>46325</v>
       </c>
@@ -2765,9 +2799,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B126" t="s">
         <v>151</v>
@@ -2779,7 +2813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>46325</v>
       </c>
@@ -2793,7 +2827,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>46312</v>
       </c>
@@ -2807,7 +2841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>46323</v>
       </c>
@@ -2821,7 +2855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>46325</v>
       </c>
@@ -2835,9 +2869,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
-        <v>46351</v>
+        <v>46341</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>155</v>
@@ -2849,7 +2883,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>46326</v>
       </c>
@@ -2863,7 +2897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>46333</v>
       </c>
@@ -2874,7 +2908,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>46336</v>
       </c>
@@ -2885,7 +2919,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>46318</v>
       </c>
@@ -2899,7 +2933,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>46326</v>
       </c>
@@ -2913,7 +2947,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>46322</v>
       </c>
@@ -2927,7 +2961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>46318</v>
       </c>
@@ -2941,7 +2975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>46322</v>
       </c>
@@ -2955,7 +2989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>46320</v>
       </c>
@@ -2967,7 +3001,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>46319</v>
       </c>
@@ -2981,7 +3015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>46336</v>
       </c>
@@ -2993,7 +3027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>46326</v>
       </c>
@@ -3005,7 +3039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="16.5" x14ac:dyDescent="0.6">
+    <row r="144" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A144" s="11">
         <v>46341</v>
       </c>
@@ -3017,12 +3051,65 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>46356</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>175</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <v>46336</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D146" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A147" s="2">
+        <v>46336</v>
+      </c>
+      <c r="B147" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="C147" s="13"/>
+      <c r="D147" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <v>46346</v>
+      </c>
+      <c r="B148" t="s">
+        <v>204</v>
+      </c>
+      <c r="D148" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>46373</v>
+      </c>
+      <c r="B149" t="s">
+        <v>205</v>
+      </c>
+      <c r="D149" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <v>46356</v>
+      </c>
+      <c r="B150" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Calendar-tasks.xlsx
+++ b/Calendar-tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntpccoin-my.sharepoint.com/personal/abhilashkaimal_ntpc_co_in/Documents/Patratu/Project Dashboard - Microsoft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1010" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DF330F2-A9E3-4452-994F-242BEA97868A}"/>
+  <xr:revisionPtr revIDLastSave="1041" documentId="11_8B4E12AF9654DCEFE06E84D54E014EBA3403EE4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90E26C02-2F58-4CCD-A592-41EFAFF3F495}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="220">
   <si>
     <t>Date</t>
   </si>
@@ -667,6 +667,36 @@
   </si>
   <si>
     <t>Delayed - 15.10.26/30.10.26</t>
+  </si>
+  <si>
+    <t>FD Fan 3B Lube oil pump trial by</t>
+  </si>
+  <si>
+    <t>Delayed - 25.10.26/31.10.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seal Oil AC and DC pumps trial </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG Lube oil and jacking oil DC PP trial by </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG Lube oil and jacking oil AC PP trial by </t>
+  </si>
+  <si>
+    <t>TVDC Readiness</t>
+  </si>
+  <si>
+    <t>BVDC Readiness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMCC Charging </t>
+  </si>
+  <si>
+    <t>220V DCDB Readiness</t>
+  </si>
+  <si>
+    <t>Delayed - 25.10.26/05.11.26</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2372,13 +2402,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>46325</v>
+        <v>46335</v>
       </c>
       <c r="B94" t="s">
         <v>120</v>
       </c>
       <c r="C94" t="s">
-        <v>59</v>
+        <v>194</v>
       </c>
       <c r="D94" t="s">
         <v>12</v>
@@ -2386,13 +2416,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>46331</v>
+        <v>46342</v>
       </c>
       <c r="B95" t="s">
         <v>121</v>
       </c>
       <c r="C95" t="s">
-        <v>59</v>
+        <v>219</v>
       </c>
       <c r="D95" t="s">
         <v>12</v>
@@ -2935,13 +2965,13 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>46326</v>
+        <v>46331</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>166</v>
       </c>
       <c r="C136" t="s">
-        <v>59</v>
+        <v>211</v>
       </c>
       <c r="D136" t="s">
         <v>12</v>
@@ -3058,6 +3088,9 @@
       <c r="B145" s="7" t="s">
         <v>175</v>
       </c>
+      <c r="D145" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="146" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
@@ -3110,6 +3143,97 @@
       </c>
       <c r="B150" t="s">
         <v>207</v>
+      </c>
+      <c r="D150" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="2">
+        <v>46342</v>
+      </c>
+      <c r="B151" t="s">
+        <v>210</v>
+      </c>
+      <c r="D151" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>46351</v>
+      </c>
+      <c r="B152" t="s">
+        <v>212</v>
+      </c>
+      <c r="D152" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <v>46348</v>
+      </c>
+      <c r="B153" t="s">
+        <v>213</v>
+      </c>
+      <c r="D153" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>46346</v>
+      </c>
+      <c r="B154" t="s">
+        <v>214</v>
+      </c>
+      <c r="D154" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="2">
+        <v>46351</v>
+      </c>
+      <c r="B155" t="s">
+        <v>215</v>
+      </c>
+      <c r="D155" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>46358</v>
+      </c>
+      <c r="B156" t="s">
+        <v>216</v>
+      </c>
+      <c r="D156" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>46356</v>
+      </c>
+      <c r="B157" t="s">
+        <v>217</v>
+      </c>
+      <c r="D157" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>46352</v>
+      </c>
+      <c r="B158" t="s">
+        <v>218</v>
+      </c>
+      <c r="D158" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
